--- a/diseases/d016/2026-2029.xlsx
+++ b/diseases/d016/2026-2029.xlsx
@@ -39398,12 +39398,12 @@
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
@@ -39428,12 +39428,12 @@
       </c>
       <c r="L220" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M220" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N220" t="n">
@@ -39476,42 +39476,42 @@
       </c>
       <c r="AV220" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW220" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX220" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY220" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ220" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA220" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB220" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC220" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -39543,12 +39543,12 @@
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
@@ -39595,87 +39595,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U221" t="inlineStr">
-        <is>
-          <t>SER_KR_ANIMAL_INFLUENZA_HUMAN_INFECTION</t>
-        </is>
-      </c>
-      <c r="AA221" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO221" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP221" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ221" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR221" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS221" t="inlineStr">
-        <is>
-          <t>SER_KR_ANIMAL_INFLUENZA_HUMAN_INFECTION</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS221" t="inlineStr"/>
       <c r="AT221" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU221" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV221" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW221" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX221" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY221" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ221" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA221" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB221" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC221" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -39702,7 +39683,7 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
@@ -39751,98 +39732,23 @@
       <c r="O222" t="n">
         <v>0</v>
       </c>
+      <c r="R222" t="n">
+        <v>0</v>
+      </c>
+      <c r="S222" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U222" t="inlineStr">
         <is>
           <t>SER_KR_ANIMAL_INFLUENZA_HUMAN_INFECTION</t>
         </is>
       </c>
-      <c r="V222" t="inlineStr">
-        <is>
-          <t>SER_KR_ANIMAL_INFLUENZA_HUMAN_INFECTION</t>
-        </is>
-      </c>
-      <c r="W222" t="inlineStr">
-        <is>
-          <t>SRC_KR_KDCA</t>
-        </is>
-      </c>
-      <c r="X222" t="inlineStr">
-        <is>
-          <t>동물인플루엔자 인체감염증</t>
-        </is>
-      </c>
-      <c r="Y222" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z222" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA222" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB222" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC222" t="inlineStr">
-        <is>
-          <t>country:KR:national</t>
-        </is>
-      </c>
-      <c r="AD222" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE222" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF222" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG222" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH222" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI222" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ222" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
-        </is>
-      </c>
-      <c r="AK222" t="inlineStr">
-        <is>
-          <t>Korea KDCA animal influenza infection in humans, retained separately from the generic novel influenza category.</t>
-        </is>
-      </c>
-      <c r="AM222" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN222" t="b">
-        <v>1</v>
       </c>
       <c r="AO222" t="inlineStr">
         <is>
@@ -39992,12 +39898,12 @@
       </c>
       <c r="U223" t="inlineStr">
         <is>
-          <t>SER_KR_NOVEL_INFLUENZA</t>
+          <t>SER_KR_ANIMAL_INFLUENZA_HUMAN_INFECTION</t>
         </is>
       </c>
       <c r="V223" t="inlineStr">
         <is>
-          <t>SER_KR_NOVEL_INFLUENZA</t>
+          <t>SER_KR_ANIMAL_INFLUENZA_HUMAN_INFECTION</t>
         </is>
       </c>
       <c r="W223" t="inlineStr">
@@ -40007,7 +39913,7 @@
       </c>
       <c r="X223" t="inlineStr">
         <is>
-          <t>신종인플루엔자</t>
+          <t>동물인플루엔자 인체감염증</t>
         </is>
       </c>
       <c r="Y223" t="inlineStr">
@@ -40072,7 +39978,7 @@
       </c>
       <c r="AK223" t="inlineStr">
         <is>
-          <t>Korea KDCA novel influenza category.</t>
+          <t>Korea KDCA animal influenza infection in humans, retained separately from the generic novel influenza category.</t>
         </is>
       </c>
       <c r="AM223" t="inlineStr">
@@ -40081,7 +39987,7 @@
         </is>
       </c>
       <c r="AN223" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO223" t="inlineStr">
         <is>
@@ -40152,6 +40058,245 @@
         </is>
       </c>
       <c r="BC223" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>D016</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>novel-influenza-a</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>Novel influenza A</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>D016</t>
+        </is>
+      </c>
+      <c r="I224" t="inlineStr">
+        <is>
+          <t>Novel influenza A</t>
+        </is>
+      </c>
+      <c r="J224" t="inlineStr">
+        <is>
+          <t>人感染新亚型流感</t>
+        </is>
+      </c>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L224" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M224" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N224" t="n">
+        <v>0</v>
+      </c>
+      <c r="O224" t="n">
+        <v>0</v>
+      </c>
+      <c r="U224" t="inlineStr">
+        <is>
+          <t>SER_KR_NOVEL_INFLUENZA</t>
+        </is>
+      </c>
+      <c r="V224" t="inlineStr">
+        <is>
+          <t>SER_KR_NOVEL_INFLUENZA</t>
+        </is>
+      </c>
+      <c r="W224" t="inlineStr">
+        <is>
+          <t>SRC_KR_KDCA</t>
+        </is>
+      </c>
+      <c r="X224" t="inlineStr">
+        <is>
+          <t>신종인플루엔자</t>
+        </is>
+      </c>
+      <c r="Y224" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z224" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA224" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB224" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC224" t="inlineStr">
+        <is>
+          <t>country:KR:national</t>
+        </is>
+      </c>
+      <c r="AD224" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE224" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF224" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG224" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH224" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI224" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ224" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK224" t="inlineStr">
+        <is>
+          <t>Korea KDCA novel influenza category.</t>
+        </is>
+      </c>
+      <c r="AM224" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN224" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO224" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP224" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ224" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR224" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS224" t="inlineStr">
+        <is>
+          <t>SER_KR_ANIMAL_INFLUENZA_HUMAN_INFECTION</t>
+        </is>
+      </c>
+      <c r="AT224" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU224" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV224" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW224" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX224" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY224" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ224" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA224" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB224" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC224" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
@@ -40273,7 +40418,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="10">
@@ -40283,7 +40428,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="11">

--- a/diseases/d016/2026-2029.xlsx
+++ b/diseases/d016/2026-2029.xlsx
@@ -36455,12 +36455,12 @@
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>China</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
@@ -36494,100 +36494,84 @@
         </is>
       </c>
       <c r="N204" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O204" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q204" t="n">
         <v>0</v>
       </c>
       <c r="R204" t="n">
-        <v>0</v>
+        <v>0.0002831028462775499</v>
       </c>
       <c r="S204" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U204" t="inlineStr">
-        <is>
-          <t>SER_KR_ANIMAL_INFLUENZA_HUMAN_INFECTION</t>
-        </is>
-      </c>
-      <c r="AA204" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO204" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP204" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ204" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR204" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS204" t="inlineStr">
-        <is>
-          <t>SER_KR_ANIMAL_INFLUENZA_HUMAN_INFECTION</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS204" t="inlineStr"/>
       <c r="AT204" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU204" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV204" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>cdc_weekly</t>
         </is>
       </c>
       <c r="AW204" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>China CDC Weekly</t>
         </is>
       </c>
       <c r="AX204" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://weekly.chinacdc.cn</t>
         </is>
       </c>
       <c r="AY204" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ204" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>cdc_weekly; nhc; pubmed</t>
         </is>
       </c>
       <c r="BA204" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
         </is>
       </c>
       <c r="BB204" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
         </is>
       </c>
       <c r="BC204" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web; web; web</t>
         </is>
       </c>
     </row>
@@ -36614,7 +36598,7 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
@@ -36663,98 +36647,23 @@
       <c r="O205" t="n">
         <v>0</v>
       </c>
+      <c r="R205" t="n">
+        <v>0</v>
+      </c>
+      <c r="S205" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U205" t="inlineStr">
         <is>
           <t>SER_KR_ANIMAL_INFLUENZA_HUMAN_INFECTION</t>
         </is>
       </c>
-      <c r="V205" t="inlineStr">
-        <is>
-          <t>SER_KR_ANIMAL_INFLUENZA_HUMAN_INFECTION</t>
-        </is>
-      </c>
-      <c r="W205" t="inlineStr">
-        <is>
-          <t>SRC_KR_KDCA</t>
-        </is>
-      </c>
-      <c r="X205" t="inlineStr">
-        <is>
-          <t>동물인플루엔자 인체감염증</t>
-        </is>
-      </c>
-      <c r="Y205" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z205" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA205" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB205" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC205" t="inlineStr">
-        <is>
-          <t>country:KR:national</t>
-        </is>
-      </c>
-      <c r="AD205" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE205" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF205" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG205" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH205" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI205" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ205" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
-        </is>
-      </c>
-      <c r="AK205" t="inlineStr">
-        <is>
-          <t>Korea KDCA animal influenza infection in humans, retained separately from the generic novel influenza category.</t>
-        </is>
-      </c>
-      <c r="AM205" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN205" t="b">
-        <v>1</v>
       </c>
       <c r="AO205" t="inlineStr">
         <is>
@@ -36904,12 +36813,12 @@
       </c>
       <c r="U206" t="inlineStr">
         <is>
-          <t>SER_KR_NOVEL_INFLUENZA</t>
+          <t>SER_KR_ANIMAL_INFLUENZA_HUMAN_INFECTION</t>
         </is>
       </c>
       <c r="V206" t="inlineStr">
         <is>
-          <t>SER_KR_NOVEL_INFLUENZA</t>
+          <t>SER_KR_ANIMAL_INFLUENZA_HUMAN_INFECTION</t>
         </is>
       </c>
       <c r="W206" t="inlineStr">
@@ -36919,7 +36828,7 @@
       </c>
       <c r="X206" t="inlineStr">
         <is>
-          <t>신종인플루엔자</t>
+          <t>동물인플루엔자 인체감염증</t>
         </is>
       </c>
       <c r="Y206" t="inlineStr">
@@ -36984,7 +36893,7 @@
       </c>
       <c r="AK206" t="inlineStr">
         <is>
-          <t>Korea KDCA novel influenza category.</t>
+          <t>Korea KDCA animal influenza infection in humans, retained separately from the generic novel influenza category.</t>
         </is>
       </c>
       <c r="AM206" t="inlineStr">
@@ -36993,7 +36902,7 @@
         </is>
       </c>
       <c r="AN206" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO206" t="inlineStr">
         <is>
@@ -37092,17 +37001,17 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
@@ -37127,7 +37036,7 @@
       </c>
       <c r="L207" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M207" t="inlineStr">
@@ -37141,76 +37050,170 @@
       <c r="O207" t="n">
         <v>0</v>
       </c>
-      <c r="R207" t="n">
-        <v>0</v>
-      </c>
-      <c r="S207" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="U207" t="inlineStr">
+        <is>
+          <t>SER_KR_NOVEL_INFLUENZA</t>
+        </is>
+      </c>
+      <c r="V207" t="inlineStr">
+        <is>
+          <t>SER_KR_NOVEL_INFLUENZA</t>
+        </is>
+      </c>
+      <c r="W207" t="inlineStr">
+        <is>
+          <t>SRC_KR_KDCA</t>
+        </is>
+      </c>
+      <c r="X207" t="inlineStr">
+        <is>
+          <t>신종인플루엔자</t>
+        </is>
+      </c>
+      <c r="Y207" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z207" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA207" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB207" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC207" t="inlineStr">
+        <is>
+          <t>country:KR:national</t>
+        </is>
+      </c>
+      <c r="AD207" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE207" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF207" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG207" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH207" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI207" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ207" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK207" t="inlineStr">
+        <is>
+          <t>Korea KDCA novel influenza category.</t>
+        </is>
+      </c>
+      <c r="AM207" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN207" t="b">
+        <v>0</v>
       </c>
       <c r="AO207" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP207" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ207" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR207" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS207" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS207" t="inlineStr">
+        <is>
+          <t>SER_KR_ANIMAL_INFLUENZA_HUMAN_INFECTION</t>
+        </is>
+      </c>
       <c r="AT207" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU207" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV207" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW207" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX207" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY207" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ207" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA207" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB207" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC207" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -37242,12 +37245,12 @@
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
@@ -37286,9 +37289,6 @@
       <c r="O208" t="n">
         <v>0</v>
       </c>
-      <c r="P208" t="n">
-        <v>0</v>
-      </c>
       <c r="R208" t="n">
         <v>0</v>
       </c>
@@ -37297,77 +37297,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA208" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO208" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP208" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ208" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS208" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_AVIAN_INFLUENZA; SER_SG_HIST_AVIAN_INFLUENZA</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR208" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS208" t="inlineStr"/>
       <c r="AT208" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU208" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV208" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW208" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX208" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY208" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ208" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA208" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB208" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC208" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -37394,7 +37385,7 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
@@ -37446,98 +37437,18 @@
       <c r="P209" t="n">
         <v>0</v>
       </c>
-      <c r="U209" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_AVIAN_INFLUENZA</t>
-        </is>
-      </c>
-      <c r="V209" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_AVIAN_INFLUENZA</t>
-        </is>
-      </c>
-      <c r="W209" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X209" t="inlineStr">
-        <is>
-          <t>Avian Influenza</t>
-        </is>
-      </c>
-      <c r="Y209" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z209" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R209" t="n">
+        <v>0</v>
+      </c>
+      <c r="S209" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA209" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB209" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC209" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD209" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE209" t="inlineStr">
-        <is>
-          <t>narrower</t>
-        </is>
-      </c>
-      <c r="AF209" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG209" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH209" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI209" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ209" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK209" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM209" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN209" t="b">
-        <v>1</v>
       </c>
       <c r="AO209" t="inlineStr">
         <is>
@@ -37631,17 +37542,17 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
@@ -37666,7 +37577,7 @@
       </c>
       <c r="L210" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M210" t="inlineStr">
@@ -37680,76 +37591,168 @@
       <c r="O210" t="n">
         <v>0</v>
       </c>
-      <c r="R210" t="n">
-        <v>0</v>
-      </c>
-      <c r="S210" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P210" t="n">
+        <v>0</v>
+      </c>
+      <c r="U210" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_AVIAN_INFLUENZA</t>
+        </is>
+      </c>
+      <c r="V210" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_AVIAN_INFLUENZA</t>
+        </is>
+      </c>
+      <c r="W210" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X210" t="inlineStr">
+        <is>
+          <t>Avian Influenza</t>
+        </is>
+      </c>
+      <c r="Y210" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z210" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA210" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB210" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC210" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD210" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE210" t="inlineStr">
+        <is>
+          <t>narrower</t>
+        </is>
+      </c>
+      <c r="AF210" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG210" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH210" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI210" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ210" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK210" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM210" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN210" t="b">
+        <v>1</v>
       </c>
       <c r="AO210" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP210" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR210" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS210" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ210" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS210" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_AVIAN_INFLUENZA; SER_SG_HIST_AVIAN_INFLUENZA</t>
+        </is>
+      </c>
       <c r="AT210" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU210" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV210" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW210" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX210" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY210" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ210" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA210" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB210" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC210" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -37781,12 +37784,12 @@
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
@@ -37825,9 +37828,6 @@
       <c r="O211" t="n">
         <v>0</v>
       </c>
-      <c r="P211" t="n">
-        <v>0</v>
-      </c>
       <c r="R211" t="n">
         <v>0</v>
       </c>
@@ -37836,77 +37836,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA211" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO211" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP211" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ211" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS211" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_AVIAN_INFLUENZA; SER_SG_HIST_AVIAN_INFLUENZA</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR211" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS211" t="inlineStr"/>
       <c r="AT211" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU211" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV211" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW211" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX211" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY211" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ211" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA211" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB211" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC211" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -37933,7 +37924,7 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
@@ -37985,98 +37976,18 @@
       <c r="P212" t="n">
         <v>0</v>
       </c>
-      <c r="U212" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_AVIAN_INFLUENZA</t>
-        </is>
-      </c>
-      <c r="V212" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_AVIAN_INFLUENZA</t>
-        </is>
-      </c>
-      <c r="W212" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X212" t="inlineStr">
-        <is>
-          <t>Avian Influenza</t>
-        </is>
-      </c>
-      <c r="Y212" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z212" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R212" t="n">
+        <v>0</v>
+      </c>
+      <c r="S212" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA212" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB212" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC212" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD212" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE212" t="inlineStr">
-        <is>
-          <t>narrower</t>
-        </is>
-      </c>
-      <c r="AF212" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG212" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH212" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI212" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ212" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK212" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM212" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN212" t="b">
-        <v>1</v>
       </c>
       <c r="AO212" t="inlineStr">
         <is>
@@ -38170,17 +38081,17 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
@@ -38205,7 +38116,7 @@
       </c>
       <c r="L213" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M213" t="inlineStr">
@@ -38219,76 +38130,168 @@
       <c r="O213" t="n">
         <v>0</v>
       </c>
-      <c r="R213" t="n">
-        <v>0</v>
-      </c>
-      <c r="S213" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P213" t="n">
+        <v>0</v>
+      </c>
+      <c r="U213" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_AVIAN_INFLUENZA</t>
+        </is>
+      </c>
+      <c r="V213" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_AVIAN_INFLUENZA</t>
+        </is>
+      </c>
+      <c r="W213" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X213" t="inlineStr">
+        <is>
+          <t>Avian Influenza</t>
+        </is>
+      </c>
+      <c r="Y213" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z213" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA213" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB213" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC213" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD213" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE213" t="inlineStr">
+        <is>
+          <t>narrower</t>
+        </is>
+      </c>
+      <c r="AF213" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG213" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH213" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI213" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ213" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK213" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM213" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN213" t="b">
+        <v>1</v>
       </c>
       <c r="AO213" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP213" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR213" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS213" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ213" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS213" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_AVIAN_INFLUENZA; SER_SG_HIST_AVIAN_INFLUENZA</t>
+        </is>
+      </c>
       <c r="AT213" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU213" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV213" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW213" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX213" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY213" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ213" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA213" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB213" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC213" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -38320,12 +38323,12 @@
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
@@ -38364,9 +38367,6 @@
       <c r="O214" t="n">
         <v>0</v>
       </c>
-      <c r="P214" t="n">
-        <v>0</v>
-      </c>
       <c r="R214" t="n">
         <v>0</v>
       </c>
@@ -38375,77 +38375,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA214" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO214" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP214" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ214" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS214" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_AVIAN_INFLUENZA; SER_SG_HIST_AVIAN_INFLUENZA</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR214" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS214" t="inlineStr"/>
       <c r="AT214" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU214" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV214" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW214" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX214" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY214" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ214" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA214" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB214" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC214" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -38472,7 +38463,7 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
@@ -38524,98 +38515,18 @@
       <c r="P215" t="n">
         <v>0</v>
       </c>
-      <c r="U215" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_AVIAN_INFLUENZA</t>
-        </is>
-      </c>
-      <c r="V215" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_AVIAN_INFLUENZA</t>
-        </is>
-      </c>
-      <c r="W215" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X215" t="inlineStr">
-        <is>
-          <t>Avian Influenza</t>
-        </is>
-      </c>
-      <c r="Y215" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z215" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R215" t="n">
+        <v>0</v>
+      </c>
+      <c r="S215" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA215" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB215" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC215" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD215" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE215" t="inlineStr">
-        <is>
-          <t>narrower</t>
-        </is>
-      </c>
-      <c r="AF215" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG215" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH215" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI215" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ215" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK215" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM215" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN215" t="b">
-        <v>1</v>
       </c>
       <c r="AO215" t="inlineStr">
         <is>
@@ -38709,17 +38620,17 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
@@ -38744,7 +38655,7 @@
       </c>
       <c r="L216" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M216" t="inlineStr">
@@ -38753,81 +38664,173 @@
         </is>
       </c>
       <c r="N216" t="n">
+        <v>0</v>
+      </c>
+      <c r="O216" t="n">
+        <v>0</v>
+      </c>
+      <c r="P216" t="n">
+        <v>0</v>
+      </c>
+      <c r="U216" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_AVIAN_INFLUENZA</t>
+        </is>
+      </c>
+      <c r="V216" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_AVIAN_INFLUENZA</t>
+        </is>
+      </c>
+      <c r="W216" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X216" t="inlineStr">
+        <is>
+          <t>Avian Influenza</t>
+        </is>
+      </c>
+      <c r="Y216" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z216" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA216" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB216" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC216" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD216" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE216" t="inlineStr">
+        <is>
+          <t>narrower</t>
+        </is>
+      </c>
+      <c r="AF216" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG216" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH216" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI216" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ216" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK216" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM216" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN216" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO216" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP216" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ216" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS216" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_AVIAN_INFLUENZA; SER_SG_HIST_AVIAN_INFLUENZA</t>
+        </is>
+      </c>
+      <c r="AT216" t="n">
         <v>2</v>
       </c>
-      <c r="O216" t="n">
-        <v>2</v>
-      </c>
-      <c r="R216" t="n">
-        <v>0.0005730076265538771</v>
-      </c>
-      <c r="S216" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AO216" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP216" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR216" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS216" t="inlineStr"/>
-      <c r="AT216" t="n">
-        <v>0</v>
-      </c>
       <c r="AU216" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV216" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW216" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX216" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY216" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ216" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA216" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB216" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC216" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -38859,12 +38862,12 @@
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
@@ -38889,7 +38892,7 @@
       </c>
       <c r="L217" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="M217" t="inlineStr">
@@ -38898,13 +38901,13 @@
         </is>
       </c>
       <c r="N217" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O217" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R217" t="n">
-        <v>0</v>
+        <v>0.0005730076265538771</v>
       </c>
       <c r="S217" t="inlineStr">
         <is>
@@ -38937,42 +38940,42 @@
       </c>
       <c r="AV217" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW217" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX217" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY217" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ217" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA217" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB217" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC217" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -39004,12 +39007,12 @@
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
@@ -39048,9 +39051,6 @@
       <c r="O218" t="n">
         <v>0</v>
       </c>
-      <c r="P218" t="n">
-        <v>0</v>
-      </c>
       <c r="R218" t="n">
         <v>0</v>
       </c>
@@ -39059,77 +39059,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA218" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO218" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP218" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ218" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS218" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_AVIAN_INFLUENZA; SER_SG_HIST_AVIAN_INFLUENZA</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR218" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS218" t="inlineStr"/>
       <c r="AT218" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU218" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV218" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW218" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX218" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY218" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ218" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA218" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB218" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC218" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -39156,7 +39147,7 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
@@ -39208,98 +39199,18 @@
       <c r="P219" t="n">
         <v>0</v>
       </c>
-      <c r="U219" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_AVIAN_INFLUENZA</t>
-        </is>
-      </c>
-      <c r="V219" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_AVIAN_INFLUENZA</t>
-        </is>
-      </c>
-      <c r="W219" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X219" t="inlineStr">
-        <is>
-          <t>Avian Influenza</t>
-        </is>
-      </c>
-      <c r="Y219" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z219" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R219" t="n">
+        <v>0</v>
+      </c>
+      <c r="S219" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA219" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB219" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC219" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD219" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE219" t="inlineStr">
-        <is>
-          <t>narrower</t>
-        </is>
-      </c>
-      <c r="AF219" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG219" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH219" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI219" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ219" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK219" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM219" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN219" t="b">
-        <v>1</v>
       </c>
       <c r="AO219" t="inlineStr">
         <is>
@@ -39393,17 +39304,17 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
@@ -39428,7 +39339,7 @@
       </c>
       <c r="L220" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M220" t="inlineStr">
@@ -39442,76 +39353,168 @@
       <c r="O220" t="n">
         <v>0</v>
       </c>
-      <c r="R220" t="n">
-        <v>0</v>
-      </c>
-      <c r="S220" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P220" t="n">
+        <v>0</v>
+      </c>
+      <c r="U220" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_AVIAN_INFLUENZA</t>
+        </is>
+      </c>
+      <c r="V220" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_AVIAN_INFLUENZA</t>
+        </is>
+      </c>
+      <c r="W220" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X220" t="inlineStr">
+        <is>
+          <t>Avian Influenza</t>
+        </is>
+      </c>
+      <c r="Y220" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z220" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA220" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB220" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC220" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD220" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE220" t="inlineStr">
+        <is>
+          <t>narrower</t>
+        </is>
+      </c>
+      <c r="AF220" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG220" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH220" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI220" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ220" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK220" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM220" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN220" t="b">
+        <v>1</v>
       </c>
       <c r="AO220" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP220" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR220" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS220" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ220" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS220" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_AVIAN_INFLUENZA; SER_SG_HIST_AVIAN_INFLUENZA</t>
+        </is>
+      </c>
       <c r="AT220" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU220" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV220" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW220" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX220" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY220" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ220" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA220" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB220" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC220" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -39543,12 +39546,12 @@
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
@@ -39573,12 +39576,12 @@
       </c>
       <c r="L221" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M221" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N221" t="n">
@@ -39621,42 +39624,42 @@
       </c>
       <c r="AV221" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW221" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX221" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY221" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ221" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA221" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB221" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC221" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -39688,12 +39691,12 @@
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
@@ -39718,12 +39721,12 @@
       </c>
       <c r="L222" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M222" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N222" t="n">
@@ -39732,6 +39735,9 @@
       <c r="O222" t="n">
         <v>0</v>
       </c>
+      <c r="P222" t="n">
+        <v>0</v>
+      </c>
       <c r="R222" t="n">
         <v>0</v>
       </c>
@@ -39740,14 +39746,9 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U222" t="inlineStr">
-        <is>
-          <t>SER_KR_ANIMAL_INFLUENZA_HUMAN_INFECTION</t>
-        </is>
-      </c>
       <c r="AA222" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO222" t="inlineStr">
@@ -39757,7 +39758,7 @@
       </c>
       <c r="AP222" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>temporal_handoff</t>
         </is>
       </c>
       <c r="AQ222" t="inlineStr">
@@ -39765,14 +39766,9 @@
           <t>parity</t>
         </is>
       </c>
-      <c r="AR222" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
       <c r="AS222" t="inlineStr">
         <is>
-          <t>SER_KR_ANIMAL_INFLUENZA_HUMAN_INFECTION</t>
+          <t>SER_SG_CDA_AVIAN_INFLUENZA; SER_SG_HIST_AVIAN_INFLUENZA</t>
         </is>
       </c>
       <c r="AT222" t="n">
@@ -39780,47 +39776,47 @@
       </c>
       <c r="AU222" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV222" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW222" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX222" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY222" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ222" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA222" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB222" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC222" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -39852,12 +39848,12 @@
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
@@ -39882,12 +39878,12 @@
       </c>
       <c r="L223" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M223" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N223" t="n">
@@ -39896,24 +39892,27 @@
       <c r="O223" t="n">
         <v>0</v>
       </c>
+      <c r="P223" t="n">
+        <v>0</v>
+      </c>
       <c r="U223" t="inlineStr">
         <is>
-          <t>SER_KR_ANIMAL_INFLUENZA_HUMAN_INFECTION</t>
+          <t>SER_SG_CDA_AVIAN_INFLUENZA</t>
         </is>
       </c>
       <c r="V223" t="inlineStr">
         <is>
-          <t>SER_KR_ANIMAL_INFLUENZA_HUMAN_INFECTION</t>
+          <t>SER_SG_CDA_AVIAN_INFLUENZA</t>
         </is>
       </c>
       <c r="W223" t="inlineStr">
         <is>
-          <t>SRC_KR_KDCA</t>
+          <t>SRC_SG_CDA_WIDB</t>
         </is>
       </c>
       <c r="X223" t="inlineStr">
         <is>
-          <t>동물인플루엔자 인체감염증</t>
+          <t>Avian Influenza</t>
         </is>
       </c>
       <c r="Y223" t="inlineStr">
@@ -39923,12 +39922,12 @@
       </c>
       <c r="Z223" t="inlineStr">
         <is>
-          <t>notification</t>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA223" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AB223" t="inlineStr">
@@ -39938,7 +39937,7 @@
       </c>
       <c r="AC223" t="inlineStr">
         <is>
-          <t>country:KR:national</t>
+          <t>country:SG:national</t>
         </is>
       </c>
       <c r="AD223" t="inlineStr">
@@ -39948,12 +39947,12 @@
       </c>
       <c r="AE223" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>narrower</t>
         </is>
       </c>
       <c r="AF223" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>conditional</t>
         </is>
       </c>
       <c r="AG223" t="inlineStr">
@@ -39973,12 +39972,12 @@
       </c>
       <c r="AJ223" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
         </is>
       </c>
       <c r="AK223" t="inlineStr">
         <is>
-          <t>Korea KDCA animal influenza infection in humans, retained separately from the generic novel influenza category.</t>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
         </is>
       </c>
       <c r="AM223" t="inlineStr">
@@ -39996,7 +39995,7 @@
       </c>
       <c r="AP223" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>temporal_handoff</t>
         </is>
       </c>
       <c r="AQ223" t="inlineStr">
@@ -40004,14 +40003,9 @@
           <t>parity</t>
         </is>
       </c>
-      <c r="AR223" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
       <c r="AS223" t="inlineStr">
         <is>
-          <t>SER_KR_ANIMAL_INFLUENZA_HUMAN_INFECTION</t>
+          <t>SER_SG_CDA_AVIAN_INFLUENZA; SER_SG_HIST_AVIAN_INFLUENZA</t>
         </is>
       </c>
       <c r="AT223" t="n">
@@ -40019,47 +40013,47 @@
       </c>
       <c r="AU223" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV223" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW223" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX223" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY223" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ223" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA223" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB223" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC223" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -40086,217 +40080,765 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>D016</t>
+        </is>
+      </c>
+      <c r="I224" t="inlineStr">
+        <is>
+          <t>Novel influenza A</t>
+        </is>
+      </c>
+      <c r="J224" t="inlineStr">
+        <is>
+          <t>人感染新亚型流感</t>
+        </is>
+      </c>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L224" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M224" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N224" t="n">
+        <v>0</v>
+      </c>
+      <c r="O224" t="n">
+        <v>0</v>
+      </c>
+      <c r="R224" t="n">
+        <v>0</v>
+      </c>
+      <c r="S224" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO224" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP224" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR224" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS224" t="inlineStr"/>
+      <c r="AT224" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU224" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV224" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW224" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="AX224" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="AY224" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ224" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA224" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="BB224" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="BC224" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>D016</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>novel-influenza-a</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>Novel influenza A</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>D016</t>
+        </is>
+      </c>
+      <c r="I225" t="inlineStr">
+        <is>
+          <t>Novel influenza A</t>
+        </is>
+      </c>
+      <c r="J225" t="inlineStr">
+        <is>
+          <t>人感染新亚型流感</t>
+        </is>
+      </c>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L225" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M225" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N225" t="n">
+        <v>0</v>
+      </c>
+      <c r="O225" t="n">
+        <v>0</v>
+      </c>
+      <c r="R225" t="n">
+        <v>0</v>
+      </c>
+      <c r="S225" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U225" t="inlineStr">
+        <is>
+          <t>SER_KR_ANIMAL_INFLUENZA_HUMAN_INFECTION</t>
+        </is>
+      </c>
+      <c r="AA225" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO225" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP225" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ225" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR225" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS225" t="inlineStr">
+        <is>
+          <t>SER_KR_ANIMAL_INFLUENZA_HUMAN_INFECTION</t>
+        </is>
+      </c>
+      <c r="AT225" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU225" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV225" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW225" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX225" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY225" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ225" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA225" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB225" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC225" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>D016</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>novel-influenza-a</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>Novel influenza A</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
           <t>source_series_observation</t>
         </is>
       </c>
-      <c r="F224" t="inlineStr">
+      <c r="F226" t="inlineStr">
         <is>
           <t>KR</t>
         </is>
       </c>
-      <c r="G224" t="inlineStr">
+      <c r="G226" t="inlineStr">
         <is>
           <t>South Korea</t>
         </is>
       </c>
-      <c r="H224" t="inlineStr">
-        <is>
-          <t>D016</t>
-        </is>
-      </c>
-      <c r="I224" t="inlineStr">
-        <is>
-          <t>Novel influenza A</t>
-        </is>
-      </c>
-      <c r="J224" t="inlineStr">
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>D016</t>
+        </is>
+      </c>
+      <c r="I226" t="inlineStr">
+        <is>
+          <t>Novel influenza A</t>
+        </is>
+      </c>
+      <c r="J226" t="inlineStr">
         <is>
           <t>人感染新亚型流感</t>
         </is>
       </c>
-      <c r="K224" t="inlineStr">
+      <c r="K226" t="inlineStr">
         <is>
           <t>Viral</t>
         </is>
       </c>
-      <c r="L224" t="inlineStr">
+      <c r="L226" t="inlineStr">
         <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="M224" t="inlineStr">
+      <c r="M226" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="N224" t="n">
-        <v>0</v>
-      </c>
-      <c r="O224" t="n">
-        <v>0</v>
-      </c>
-      <c r="U224" t="inlineStr">
+      <c r="N226" t="n">
+        <v>0</v>
+      </c>
+      <c r="O226" t="n">
+        <v>0</v>
+      </c>
+      <c r="U226" t="inlineStr">
+        <is>
+          <t>SER_KR_ANIMAL_INFLUENZA_HUMAN_INFECTION</t>
+        </is>
+      </c>
+      <c r="V226" t="inlineStr">
+        <is>
+          <t>SER_KR_ANIMAL_INFLUENZA_HUMAN_INFECTION</t>
+        </is>
+      </c>
+      <c r="W226" t="inlineStr">
+        <is>
+          <t>SRC_KR_KDCA</t>
+        </is>
+      </c>
+      <c r="X226" t="inlineStr">
+        <is>
+          <t>동물인플루엔자 인체감염증</t>
+        </is>
+      </c>
+      <c r="Y226" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z226" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA226" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB226" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC226" t="inlineStr">
+        <is>
+          <t>country:KR:national</t>
+        </is>
+      </c>
+      <c r="AD226" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE226" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF226" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG226" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH226" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI226" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ226" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK226" t="inlineStr">
+        <is>
+          <t>Korea KDCA animal influenza infection in humans, retained separately from the generic novel influenza category.</t>
+        </is>
+      </c>
+      <c r="AM226" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN226" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO226" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP226" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ226" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR226" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS226" t="inlineStr">
+        <is>
+          <t>SER_KR_ANIMAL_INFLUENZA_HUMAN_INFECTION</t>
+        </is>
+      </c>
+      <c r="AT226" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU226" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV226" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW226" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX226" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY226" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ226" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA226" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB226" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC226" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>D016</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>novel-influenza-a</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>Novel influenza A</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>D016</t>
+        </is>
+      </c>
+      <c r="I227" t="inlineStr">
+        <is>
+          <t>Novel influenza A</t>
+        </is>
+      </c>
+      <c r="J227" t="inlineStr">
+        <is>
+          <t>人感染新亚型流感</t>
+        </is>
+      </c>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L227" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M227" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N227" t="n">
+        <v>0</v>
+      </c>
+      <c r="O227" t="n">
+        <v>0</v>
+      </c>
+      <c r="U227" t="inlineStr">
         <is>
           <t>SER_KR_NOVEL_INFLUENZA</t>
         </is>
       </c>
-      <c r="V224" t="inlineStr">
+      <c r="V227" t="inlineStr">
         <is>
           <t>SER_KR_NOVEL_INFLUENZA</t>
         </is>
       </c>
-      <c r="W224" t="inlineStr">
+      <c r="W227" t="inlineStr">
         <is>
           <t>SRC_KR_KDCA</t>
         </is>
       </c>
-      <c r="X224" t="inlineStr">
+      <c r="X227" t="inlineStr">
         <is>
           <t>신종인플루엔자</t>
         </is>
       </c>
-      <c r="Y224" t="inlineStr">
+      <c r="Y227" t="inlineStr">
         <is>
           <t>case_notifications</t>
         </is>
       </c>
-      <c r="Z224" t="inlineStr">
+      <c r="Z227" t="inlineStr">
         <is>
           <t>notification</t>
         </is>
       </c>
-      <c r="AA224" t="inlineStr">
+      <c r="AA227" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB224" t="inlineStr">
+      <c r="AB227" t="inlineStr">
         <is>
           <t>count</t>
         </is>
       </c>
-      <c r="AC224" t="inlineStr">
+      <c r="AC227" t="inlineStr">
         <is>
           <t>country:KR:national</t>
         </is>
       </c>
-      <c r="AD224" t="inlineStr">
+      <c r="AD227" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE224" t="inlineStr">
+      <c r="AE227" t="inlineStr">
         <is>
           <t>exact</t>
         </is>
       </c>
-      <c r="AF224" t="inlineStr">
+      <c r="AF227" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="AG224" t="inlineStr">
+      <c r="AG227" t="inlineStr">
         <is>
           <t>non_additive</t>
         </is>
       </c>
-      <c r="AH224" t="inlineStr">
+      <c r="AH227" t="inlineStr">
         <is>
           <t>active</t>
         </is>
       </c>
-      <c r="AI224" t="inlineStr">
+      <c r="AI227" t="inlineStr">
         <is>
           <t>missing_is_unknown</t>
         </is>
       </c>
-      <c r="AJ224" t="inlineStr">
+      <c r="AJ227" t="inlineStr">
         <is>
           <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
-      <c r="AK224" t="inlineStr">
+      <c r="AK227" t="inlineStr">
         <is>
           <t>Korea KDCA novel influenza category.</t>
         </is>
       </c>
-      <c r="AM224" t="inlineStr">
+      <c r="AM227" t="inlineStr">
         <is>
           <t>provisional; raw</t>
         </is>
       </c>
-      <c r="AN224" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO224" t="inlineStr">
+      <c r="AN227" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO227" t="inlineStr">
         <is>
           <t>series_registry</t>
         </is>
       </c>
-      <c r="AP224" t="inlineStr">
+      <c r="AP227" t="inlineStr">
         <is>
           <t>representative_series</t>
         </is>
       </c>
-      <c r="AQ224" t="inlineStr">
+      <c r="AQ227" t="inlineStr">
         <is>
           <t>parity</t>
         </is>
       </c>
-      <c r="AR224" t="inlineStr">
+      <c r="AR227" t="inlineStr">
         <is>
           <t>non_additive_series_not_rolled_up</t>
         </is>
       </c>
-      <c r="AS224" t="inlineStr">
+      <c r="AS227" t="inlineStr">
         <is>
           <t>SER_KR_ANIMAL_INFLUENZA_HUMAN_INFECTION</t>
         </is>
       </c>
-      <c r="AT224" t="n">
+      <c r="AT227" t="n">
         <v>2</v>
       </c>
-      <c r="AU224" t="inlineStr">
+      <c r="AU227" t="inlineStr">
         <is>
           <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
-      <c r="AV224" t="inlineStr">
+      <c r="AV227" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="AW224" t="inlineStr">
+      <c r="AW227" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="AX224" t="inlineStr">
+      <c r="AX227" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="AY224" t="inlineStr">
+      <c r="AY227" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
       </c>
-      <c r="AZ224" t="inlineStr">
+      <c r="AZ227" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="BA224" t="inlineStr">
+      <c r="BA227" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="BB224" t="inlineStr">
+      <c r="BB227" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="BC224" t="inlineStr">
+      <c r="BC227" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
@@ -40418,7 +40960,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="10">
@@ -40428,7 +40970,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>223</v>
+        <v>226</v>
       </c>
     </row>
     <row r="11">
@@ -40448,7 +40990,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="13">
@@ -40480,7 +41022,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d016/2026-2029.xlsx
+++ b/diseases/d016/2026-2029.xlsx
@@ -40844,6 +40844,151 @@
         </is>
       </c>
     </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>D016</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>novel-influenza-a</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>Novel influenza A</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>D016</t>
+        </is>
+      </c>
+      <c r="I228" t="inlineStr">
+        <is>
+          <t>Novel influenza A</t>
+        </is>
+      </c>
+      <c r="J228" t="inlineStr">
+        <is>
+          <t>人感染新亚型流感</t>
+        </is>
+      </c>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L228" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M228" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N228" t="n">
+        <v>0</v>
+      </c>
+      <c r="O228" t="n">
+        <v>0</v>
+      </c>
+      <c r="R228" t="n">
+        <v>0</v>
+      </c>
+      <c r="S228" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO228" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP228" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR228" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS228" t="inlineStr"/>
+      <c r="AT228" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU228" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV228" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW228" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX228" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY228" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ228" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA228" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB228" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC228" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -40877,7 +41022,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -40960,7 +41105,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="10">
@@ -40970,7 +41115,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="11">

--- a/diseases/d016/2026-2029.xlsx
+++ b/diseases/d016/2026-2029.xlsx
@@ -40989,6 +40989,400 @@
         </is>
       </c>
     </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>D016</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>novel-influenza-a</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>Novel influenza A</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>D016</t>
+        </is>
+      </c>
+      <c r="I229" t="inlineStr">
+        <is>
+          <t>Novel influenza A</t>
+        </is>
+      </c>
+      <c r="J229" t="inlineStr">
+        <is>
+          <t>人感染新亚型流感</t>
+        </is>
+      </c>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L229" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M229" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N229" t="n">
+        <v>0</v>
+      </c>
+      <c r="O229" t="n">
+        <v>0</v>
+      </c>
+      <c r="P229" t="n">
+        <v>0</v>
+      </c>
+      <c r="R229" t="n">
+        <v>0</v>
+      </c>
+      <c r="S229" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA229" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO229" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP229" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ229" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS229" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_AVIAN_INFLUENZA; SER_SG_HIST_AVIAN_INFLUENZA</t>
+        </is>
+      </c>
+      <c r="AT229" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU229" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV229" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW229" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX229" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY229" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ229" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA229" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB229" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC229" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>D016</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>novel-influenza-a</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>Novel influenza A</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>D016</t>
+        </is>
+      </c>
+      <c r="I230" t="inlineStr">
+        <is>
+          <t>Novel influenza A</t>
+        </is>
+      </c>
+      <c r="J230" t="inlineStr">
+        <is>
+          <t>人感染新亚型流感</t>
+        </is>
+      </c>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L230" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M230" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N230" t="n">
+        <v>0</v>
+      </c>
+      <c r="O230" t="n">
+        <v>0</v>
+      </c>
+      <c r="P230" t="n">
+        <v>0</v>
+      </c>
+      <c r="U230" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_AVIAN_INFLUENZA</t>
+        </is>
+      </c>
+      <c r="V230" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_AVIAN_INFLUENZA</t>
+        </is>
+      </c>
+      <c r="W230" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X230" t="inlineStr">
+        <is>
+          <t>Avian Influenza</t>
+        </is>
+      </c>
+      <c r="Y230" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z230" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA230" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB230" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC230" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD230" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE230" t="inlineStr">
+        <is>
+          <t>narrower</t>
+        </is>
+      </c>
+      <c r="AF230" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG230" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH230" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI230" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ230" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK230" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM230" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN230" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO230" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP230" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ230" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS230" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_AVIAN_INFLUENZA; SER_SG_HIST_AVIAN_INFLUENZA</t>
+        </is>
+      </c>
+      <c r="AT230" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU230" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV230" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW230" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX230" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY230" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ230" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA230" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB230" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC230" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -41105,7 +41499,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="10">
@@ -41115,7 +41509,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>227</v>
+        <v>229</v>
       </c>
     </row>
     <row r="11">
@@ -41135,7 +41529,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="13">

--- a/diseases/d016/2026-2029.xlsx
+++ b/diseases/d016/2026-2029.xlsx
@@ -1992,7 +1992,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
@@ -2231,7 +2231,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -6528,7 +6528,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -6767,7 +6767,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
@@ -10916,7 +10916,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -11155,7 +11155,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK58" t="inlineStr">
@@ -15843,7 +15843,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK84" t="inlineStr">
@@ -16082,7 +16082,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -20228,7 +20228,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK108" t="inlineStr">
@@ -20467,7 +20467,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
@@ -26439,7 +26439,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK144" t="inlineStr">
@@ -26678,7 +26678,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK145" t="inlineStr">
@@ -31936,7 +31936,7 @@
       </c>
       <c r="AJ176" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK176" t="inlineStr">
@@ -32175,7 +32175,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK177" t="inlineStr">
@@ -36598,17 +36598,17 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
@@ -36647,17 +36647,34 @@
       <c r="O205" t="n">
         <v>0</v>
       </c>
-      <c r="R205" t="n">
-        <v>0</v>
-      </c>
-      <c r="S205" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U205" t="inlineStr">
         <is>
-          <t>SER_KR_ANIMAL_INFLUENZA_HUMAN_INFECTION</t>
+          <t>SER_HK_NOVEL_INFLUENZA_H5</t>
+        </is>
+      </c>
+      <c r="V205" t="inlineStr">
+        <is>
+          <t>SER_HK_NOVEL_INFLUENZA_H5</t>
+        </is>
+      </c>
+      <c r="W205" t="inlineStr">
+        <is>
+          <t>SRC_HK_CHP</t>
+        </is>
+      </c>
+      <c r="X205" t="inlineStr">
+        <is>
+          <t>Influenza A - Influenza A (H5)</t>
+        </is>
+      </c>
+      <c r="Y205" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z205" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA205" t="inlineStr">
@@ -36665,77 +36682,126 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB205" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC205" t="inlineStr">
+        <is>
+          <t>country:HK:national</t>
+        </is>
+      </c>
+      <c r="AD205" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE205" t="inlineStr">
+        <is>
+          <t>narrower</t>
+        </is>
+      </c>
+      <c r="AF205" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG205" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH205" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI205" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ205" t="inlineStr">
+        <is>
+          <t>HK_CHP_H5_current</t>
+        </is>
+      </c>
+      <c r="AK205" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP H5 novel influenza A category.</t>
+        </is>
+      </c>
+      <c r="AM205" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN205" t="b">
+        <v>0</v>
+      </c>
       <c r="AO205" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>source_observations_only</t>
         </is>
       </c>
       <c r="AP205" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>no_eligible_public_projection</t>
         </is>
       </c>
       <c r="AQ205" t="inlineStr">
         <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AR205" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS205" t="inlineStr">
-        <is>
-          <t>SER_KR_ANIMAL_INFLUENZA_HUMAN_INFECTION</t>
-        </is>
-      </c>
+          <t>source_observations_only</t>
+        </is>
+      </c>
+      <c r="AS205" t="inlineStr"/>
       <c r="AT205" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="AU205" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
         </is>
       </c>
       <c r="AV205" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW205" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX205" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY205" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ205" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA205" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB205" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC205" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -36767,12 +36833,12 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
@@ -36813,22 +36879,22 @@
       </c>
       <c r="U206" t="inlineStr">
         <is>
-          <t>SER_KR_ANIMAL_INFLUENZA_HUMAN_INFECTION</t>
+          <t>SER_HK_NOVEL_INFLUENZA_H7</t>
         </is>
       </c>
       <c r="V206" t="inlineStr">
         <is>
-          <t>SER_KR_ANIMAL_INFLUENZA_HUMAN_INFECTION</t>
+          <t>SER_HK_NOVEL_INFLUENZA_H7</t>
         </is>
       </c>
       <c r="W206" t="inlineStr">
         <is>
-          <t>SRC_KR_KDCA</t>
+          <t>SRC_HK_CHP</t>
         </is>
       </c>
       <c r="X206" t="inlineStr">
         <is>
-          <t>동물인플루엔자 인체감염증</t>
+          <t>Influenza A - Influenza A (H7)</t>
         </is>
       </c>
       <c r="Y206" t="inlineStr">
@@ -36853,7 +36919,7 @@
       </c>
       <c r="AC206" t="inlineStr">
         <is>
-          <t>country:KR:national</t>
+          <t>country:HK:national</t>
         </is>
       </c>
       <c r="AD206" t="inlineStr">
@@ -36863,12 +36929,12 @@
       </c>
       <c r="AE206" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>narrower</t>
         </is>
       </c>
       <c r="AF206" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>conditional</t>
         </is>
       </c>
       <c r="AG206" t="inlineStr">
@@ -36888,12 +36954,12 @@
       </c>
       <c r="AJ206" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>HK_CHP_H7_current</t>
         </is>
       </c>
       <c r="AK206" t="inlineStr">
         <is>
-          <t>Korea KDCA animal influenza infection in humans, retained separately from the generic novel influenza category.</t>
+          <t>Hong Kong, China CHP H7 novel influenza A category.</t>
         </is>
       </c>
       <c r="AM206" t="inlineStr">
@@ -36902,79 +36968,70 @@
         </is>
       </c>
       <c r="AN206" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO206" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>source_observations_only</t>
         </is>
       </c>
       <c r="AP206" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>no_eligible_public_projection</t>
         </is>
       </c>
       <c r="AQ206" t="inlineStr">
         <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AR206" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS206" t="inlineStr">
-        <is>
-          <t>SER_KR_ANIMAL_INFLUENZA_HUMAN_INFECTION</t>
-        </is>
-      </c>
+          <t>source_observations_only</t>
+        </is>
+      </c>
+      <c r="AS206" t="inlineStr"/>
       <c r="AT206" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="AU206" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
         </is>
       </c>
       <c r="AV206" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW206" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX206" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY206" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ206" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA206" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB206" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC206" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -37006,12 +37063,12 @@
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
@@ -37052,22 +37109,22 @@
       </c>
       <c r="U207" t="inlineStr">
         <is>
-          <t>SER_KR_NOVEL_INFLUENZA</t>
+          <t>SER_HK_NOVEL_INFLUENZA_OTHERS</t>
         </is>
       </c>
       <c r="V207" t="inlineStr">
         <is>
-          <t>SER_KR_NOVEL_INFLUENZA</t>
+          <t>SER_HK_NOVEL_INFLUENZA_OTHERS</t>
         </is>
       </c>
       <c r="W207" t="inlineStr">
         <is>
-          <t>SRC_KR_KDCA</t>
+          <t>SRC_HK_CHP</t>
         </is>
       </c>
       <c r="X207" t="inlineStr">
         <is>
-          <t>신종인플루엔자</t>
+          <t>Novel influenza A infection - Others</t>
         </is>
       </c>
       <c r="Y207" t="inlineStr">
@@ -37092,7 +37149,7 @@
       </c>
       <c r="AC207" t="inlineStr">
         <is>
-          <t>country:KR:national</t>
+          <t>country:HK:national</t>
         </is>
       </c>
       <c r="AD207" t="inlineStr">
@@ -37102,12 +37159,12 @@
       </c>
       <c r="AE207" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>narrower</t>
         </is>
       </c>
       <c r="AF207" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>conditional</t>
         </is>
       </c>
       <c r="AG207" t="inlineStr">
@@ -37127,12 +37184,12 @@
       </c>
       <c r="AJ207" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>HK_CHP_other_current</t>
         </is>
       </c>
       <c r="AK207" t="inlineStr">
         <is>
-          <t>Korea KDCA novel influenza category.</t>
+          <t>Hong Kong, China CHP residual novel influenza A category.</t>
         </is>
       </c>
       <c r="AM207" t="inlineStr">
@@ -37145,75 +37202,66 @@
       </c>
       <c r="AO207" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>source_observations_only</t>
         </is>
       </c>
       <c r="AP207" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>no_eligible_public_projection</t>
         </is>
       </c>
       <c r="AQ207" t="inlineStr">
         <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AR207" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS207" t="inlineStr">
-        <is>
-          <t>SER_KR_ANIMAL_INFLUENZA_HUMAN_INFECTION</t>
-        </is>
-      </c>
+          <t>source_observations_only</t>
+        </is>
+      </c>
+      <c r="AS207" t="inlineStr"/>
       <c r="AT207" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="AU207" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
         </is>
       </c>
       <c r="AV207" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW207" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX207" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY207" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ207" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA207" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB207" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC207" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -37245,12 +37293,12 @@
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
@@ -37275,7 +37323,7 @@
       </c>
       <c r="L208" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M208" t="inlineStr">
@@ -37297,68 +37345,87 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U208" t="inlineStr">
+        <is>
+          <t>SER_KR_ANIMAL_INFLUENZA_HUMAN_INFECTION</t>
+        </is>
+      </c>
+      <c r="AA208" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO208" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP208" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ208" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR208" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS208" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS208" t="inlineStr">
+        <is>
+          <t>SER_KR_ANIMAL_INFLUENZA_HUMAN_INFECTION</t>
+        </is>
+      </c>
       <c r="AT208" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU208" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV208" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW208" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX208" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY208" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ208" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA208" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB208" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC208" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -37385,17 +37452,17 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
@@ -37420,7 +37487,7 @@
       </c>
       <c r="L209" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M209" t="inlineStr">
@@ -37434,21 +37501,98 @@
       <c r="O209" t="n">
         <v>0</v>
       </c>
-      <c r="P209" t="n">
-        <v>0</v>
-      </c>
-      <c r="R209" t="n">
-        <v>0</v>
-      </c>
-      <c r="S209" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+      <c r="U209" t="inlineStr">
+        <is>
+          <t>SER_KR_ANIMAL_INFLUENZA_HUMAN_INFECTION</t>
+        </is>
+      </c>
+      <c r="V209" t="inlineStr">
+        <is>
+          <t>SER_KR_ANIMAL_INFLUENZA_HUMAN_INFECTION</t>
+        </is>
+      </c>
+      <c r="W209" t="inlineStr">
+        <is>
+          <t>SRC_KR_KDCA</t>
+        </is>
+      </c>
+      <c r="X209" t="inlineStr">
+        <is>
+          <t>동물인플루엔자 인체감염증</t>
+        </is>
+      </c>
+      <c r="Y209" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z209" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA209" t="inlineStr">
         <is>
-          <t>weekly</t>
-        </is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB209" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC209" t="inlineStr">
+        <is>
+          <t>country:KR:national</t>
+        </is>
+      </c>
+      <c r="AD209" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE209" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF209" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG209" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH209" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI209" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ209" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK209" t="inlineStr">
+        <is>
+          <t>Korea KDCA animal influenza infection in humans, retained separately from the generic novel influenza category.</t>
+        </is>
+      </c>
+      <c r="AM209" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN209" t="b">
+        <v>1</v>
       </c>
       <c r="AO209" t="inlineStr">
         <is>
@@ -37457,7 +37601,7 @@
       </c>
       <c r="AP209" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ209" t="inlineStr">
@@ -37465,9 +37609,14 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR209" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS209" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_AVIAN_INFLUENZA; SER_SG_HIST_AVIAN_INFLUENZA</t>
+          <t>SER_KR_ANIMAL_INFLUENZA_HUMAN_INFECTION</t>
         </is>
       </c>
       <c r="AT209" t="n">
@@ -37475,47 +37624,47 @@
       </c>
       <c r="AU209" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV209" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW209" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX209" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY209" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ209" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA209" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB209" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC209" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -37547,12 +37696,12 @@
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
@@ -37577,7 +37726,7 @@
       </c>
       <c r="L210" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M210" t="inlineStr">
@@ -37591,27 +37740,24 @@
       <c r="O210" t="n">
         <v>0</v>
       </c>
-      <c r="P210" t="n">
-        <v>0</v>
-      </c>
       <c r="U210" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_AVIAN_INFLUENZA</t>
+          <t>SER_KR_NOVEL_INFLUENZA</t>
         </is>
       </c>
       <c r="V210" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_AVIAN_INFLUENZA</t>
+          <t>SER_KR_NOVEL_INFLUENZA</t>
         </is>
       </c>
       <c r="W210" t="inlineStr">
         <is>
-          <t>SRC_SG_CDA_WIDB</t>
+          <t>SRC_KR_KDCA</t>
         </is>
       </c>
       <c r="X210" t="inlineStr">
         <is>
-          <t>Avian Influenza</t>
+          <t>신종인플루엔자</t>
         </is>
       </c>
       <c r="Y210" t="inlineStr">
@@ -37621,12 +37767,12 @@
       </c>
       <c r="Z210" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_surveillance</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA210" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AB210" t="inlineStr">
@@ -37636,7 +37782,7 @@
       </c>
       <c r="AC210" t="inlineStr">
         <is>
-          <t>country:SG:national</t>
+          <t>country:KR:national</t>
         </is>
       </c>
       <c r="AD210" t="inlineStr">
@@ -37646,12 +37792,12 @@
       </c>
       <c r="AE210" t="inlineStr">
         <is>
-          <t>narrower</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="AF210" t="inlineStr">
         <is>
-          <t>conditional</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AG210" t="inlineStr">
@@ -37671,12 +37817,12 @@
       </c>
       <c r="AJ210" t="inlineStr">
         <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK210" t="inlineStr">
         <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+          <t>Korea KDCA novel influenza category.</t>
         </is>
       </c>
       <c r="AM210" t="inlineStr">
@@ -37685,7 +37831,7 @@
         </is>
       </c>
       <c r="AN210" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO210" t="inlineStr">
         <is>
@@ -37694,7 +37840,7 @@
       </c>
       <c r="AP210" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ210" t="inlineStr">
@@ -37702,9 +37848,14 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR210" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS210" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_AVIAN_INFLUENZA; SER_SG_HIST_AVIAN_INFLUENZA</t>
+          <t>SER_KR_ANIMAL_INFLUENZA_HUMAN_INFECTION</t>
         </is>
       </c>
       <c r="AT210" t="n">
@@ -37712,47 +37863,47 @@
       </c>
       <c r="AU210" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV210" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW210" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX210" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY210" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ210" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA210" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB210" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC210" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -37814,7 +37965,7 @@
       </c>
       <c r="L211" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M211" t="inlineStr">
@@ -37959,7 +38110,7 @@
       </c>
       <c r="L212" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M212" t="inlineStr">
@@ -38116,7 +38267,7 @@
       </c>
       <c r="L213" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M213" t="inlineStr">
@@ -38353,7 +38504,7 @@
       </c>
       <c r="L214" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M214" t="inlineStr">
@@ -38498,7 +38649,7 @@
       </c>
       <c r="L215" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M215" t="inlineStr">
@@ -38655,7 +38806,7 @@
       </c>
       <c r="L216" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M216" t="inlineStr">
@@ -38862,12 +39013,12 @@
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
@@ -38892,7 +39043,7 @@
       </c>
       <c r="L217" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M217" t="inlineStr">
@@ -38901,13 +39052,13 @@
         </is>
       </c>
       <c r="N217" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O217" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R217" t="n">
-        <v>0.0005730076265538771</v>
+        <v>0</v>
       </c>
       <c r="S217" t="inlineStr">
         <is>
@@ -38940,42 +39091,42 @@
       </c>
       <c r="AV217" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW217" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX217" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY217" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ217" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA217" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB217" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC217" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -39007,12 +39158,12 @@
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
@@ -39037,7 +39188,7 @@
       </c>
       <c r="L218" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M218" t="inlineStr">
@@ -39051,6 +39202,9 @@
       <c r="O218" t="n">
         <v>0</v>
       </c>
+      <c r="P218" t="n">
+        <v>0</v>
+      </c>
       <c r="R218" t="n">
         <v>0</v>
       </c>
@@ -39059,68 +39213,77 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA218" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO218" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP218" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR218" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS218" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ218" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS218" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_AVIAN_INFLUENZA; SER_SG_HIST_AVIAN_INFLUENZA</t>
+        </is>
+      </c>
       <c r="AT218" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU218" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV218" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW218" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX218" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY218" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ218" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA218" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB218" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC218" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -39147,7 +39310,7 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
@@ -39182,7 +39345,7 @@
       </c>
       <c r="L219" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M219" t="inlineStr">
@@ -39199,18 +39362,98 @@
       <c r="P219" t="n">
         <v>0</v>
       </c>
-      <c r="R219" t="n">
-        <v>0</v>
-      </c>
-      <c r="S219" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+      <c r="U219" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_AVIAN_INFLUENZA</t>
+        </is>
+      </c>
+      <c r="V219" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_AVIAN_INFLUENZA</t>
+        </is>
+      </c>
+      <c r="W219" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X219" t="inlineStr">
+        <is>
+          <t>Avian Influenza</t>
+        </is>
+      </c>
+      <c r="Y219" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z219" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA219" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB219" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC219" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD219" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE219" t="inlineStr">
+        <is>
+          <t>narrower</t>
+        </is>
+      </c>
+      <c r="AF219" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG219" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH219" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI219" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ219" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK219" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM219" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN219" t="b">
+        <v>1</v>
       </c>
       <c r="AO219" t="inlineStr">
         <is>
@@ -39304,17 +39547,17 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
@@ -39339,7 +39582,7 @@
       </c>
       <c r="L220" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="M220" t="inlineStr">
@@ -39348,173 +39591,81 @@
         </is>
       </c>
       <c r="N220" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O220" t="n">
-        <v>0</v>
-      </c>
-      <c r="P220" t="n">
-        <v>0</v>
-      </c>
-      <c r="U220" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_AVIAN_INFLUENZA</t>
-        </is>
-      </c>
-      <c r="V220" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_AVIAN_INFLUENZA</t>
-        </is>
-      </c>
-      <c r="W220" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X220" t="inlineStr">
-        <is>
-          <t>Avian Influenza</t>
-        </is>
-      </c>
-      <c r="Y220" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z220" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA220" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB220" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC220" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD220" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE220" t="inlineStr">
-        <is>
-          <t>narrower</t>
-        </is>
-      </c>
-      <c r="AF220" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG220" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH220" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI220" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ220" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK220" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM220" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN220" t="b">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="R220" t="n">
+        <v>0.0005730076265538771</v>
+      </c>
+      <c r="S220" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO220" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP220" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ220" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS220" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_AVIAN_INFLUENZA; SER_SG_HIST_AVIAN_INFLUENZA</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR220" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS220" t="inlineStr"/>
       <c r="AT220" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU220" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV220" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW220" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX220" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY220" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ220" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA220" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB220" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC220" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -39576,7 +39727,7 @@
       </c>
       <c r="L221" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M221" t="inlineStr">
@@ -39721,7 +39872,7 @@
       </c>
       <c r="L222" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M222" t="inlineStr">
@@ -39878,7 +40029,7 @@
       </c>
       <c r="L223" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M223" t="inlineStr">
@@ -40085,12 +40236,12 @@
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
@@ -40115,12 +40266,12 @@
       </c>
       <c r="L224" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M224" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N224" t="n">
@@ -40163,42 +40314,42 @@
       </c>
       <c r="AV224" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW224" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX224" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY224" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ224" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA224" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB224" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC224" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -40230,12 +40381,12 @@
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
@@ -40260,12 +40411,12 @@
       </c>
       <c r="L225" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M225" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N225" t="n">
@@ -40274,6 +40425,9 @@
       <c r="O225" t="n">
         <v>0</v>
       </c>
+      <c r="P225" t="n">
+        <v>0</v>
+      </c>
       <c r="R225" t="n">
         <v>0</v>
       </c>
@@ -40282,14 +40436,9 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U225" t="inlineStr">
-        <is>
-          <t>SER_KR_ANIMAL_INFLUENZA_HUMAN_INFECTION</t>
-        </is>
-      </c>
       <c r="AA225" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO225" t="inlineStr">
@@ -40299,7 +40448,7 @@
       </c>
       <c r="AP225" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>temporal_handoff</t>
         </is>
       </c>
       <c r="AQ225" t="inlineStr">
@@ -40307,14 +40456,9 @@
           <t>parity</t>
         </is>
       </c>
-      <c r="AR225" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
       <c r="AS225" t="inlineStr">
         <is>
-          <t>SER_KR_ANIMAL_INFLUENZA_HUMAN_INFECTION</t>
+          <t>SER_SG_CDA_AVIAN_INFLUENZA; SER_SG_HIST_AVIAN_INFLUENZA</t>
         </is>
       </c>
       <c r="AT225" t="n">
@@ -40322,47 +40466,47 @@
       </c>
       <c r="AU225" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV225" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW225" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX225" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY225" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ225" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA225" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB225" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC225" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -40394,12 +40538,12 @@
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
@@ -40424,12 +40568,12 @@
       </c>
       <c r="L226" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M226" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N226" t="n">
@@ -40438,24 +40582,27 @@
       <c r="O226" t="n">
         <v>0</v>
       </c>
+      <c r="P226" t="n">
+        <v>0</v>
+      </c>
       <c r="U226" t="inlineStr">
         <is>
-          <t>SER_KR_ANIMAL_INFLUENZA_HUMAN_INFECTION</t>
+          <t>SER_SG_CDA_AVIAN_INFLUENZA</t>
         </is>
       </c>
       <c r="V226" t="inlineStr">
         <is>
-          <t>SER_KR_ANIMAL_INFLUENZA_HUMAN_INFECTION</t>
+          <t>SER_SG_CDA_AVIAN_INFLUENZA</t>
         </is>
       </c>
       <c r="W226" t="inlineStr">
         <is>
-          <t>SRC_KR_KDCA</t>
+          <t>SRC_SG_CDA_WIDB</t>
         </is>
       </c>
       <c r="X226" t="inlineStr">
         <is>
-          <t>동물인플루엔자 인체감염증</t>
+          <t>Avian Influenza</t>
         </is>
       </c>
       <c r="Y226" t="inlineStr">
@@ -40465,12 +40612,12 @@
       </c>
       <c r="Z226" t="inlineStr">
         <is>
-          <t>notification</t>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA226" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AB226" t="inlineStr">
@@ -40480,7 +40627,7 @@
       </c>
       <c r="AC226" t="inlineStr">
         <is>
-          <t>country:KR:national</t>
+          <t>country:SG:national</t>
         </is>
       </c>
       <c r="AD226" t="inlineStr">
@@ -40490,12 +40637,12 @@
       </c>
       <c r="AE226" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>narrower</t>
         </is>
       </c>
       <c r="AF226" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>conditional</t>
         </is>
       </c>
       <c r="AG226" t="inlineStr">
@@ -40515,12 +40662,12 @@
       </c>
       <c r="AJ226" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
         </is>
       </c>
       <c r="AK226" t="inlineStr">
         <is>
-          <t>Korea KDCA animal influenza infection in humans, retained separately from the generic novel influenza category.</t>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
         </is>
       </c>
       <c r="AM226" t="inlineStr">
@@ -40538,7 +40685,7 @@
       </c>
       <c r="AP226" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>temporal_handoff</t>
         </is>
       </c>
       <c r="AQ226" t="inlineStr">
@@ -40546,14 +40693,9 @@
           <t>parity</t>
         </is>
       </c>
-      <c r="AR226" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
       <c r="AS226" t="inlineStr">
         <is>
-          <t>SER_KR_ANIMAL_INFLUENZA_HUMAN_INFECTION</t>
+          <t>SER_SG_CDA_AVIAN_INFLUENZA; SER_SG_HIST_AVIAN_INFLUENZA</t>
         </is>
       </c>
       <c r="AT226" t="n">
@@ -40561,47 +40703,47 @@
       </c>
       <c r="AU226" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV226" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW226" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX226" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY226" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ226" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA226" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB226" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC226" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -40628,17 +40770,17 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
@@ -40677,170 +40819,76 @@
       <c r="O227" t="n">
         <v>0</v>
       </c>
-      <c r="U227" t="inlineStr">
-        <is>
-          <t>SER_KR_NOVEL_INFLUENZA</t>
-        </is>
-      </c>
-      <c r="V227" t="inlineStr">
-        <is>
-          <t>SER_KR_NOVEL_INFLUENZA</t>
-        </is>
-      </c>
-      <c r="W227" t="inlineStr">
-        <is>
-          <t>SRC_KR_KDCA</t>
-        </is>
-      </c>
-      <c r="X227" t="inlineStr">
-        <is>
-          <t>신종인플루엔자</t>
-        </is>
-      </c>
-      <c r="Y227" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z227" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
-      <c r="AA227" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB227" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC227" t="inlineStr">
-        <is>
-          <t>country:KR:national</t>
-        </is>
-      </c>
-      <c r="AD227" t="inlineStr">
+      <c r="R227" t="n">
+        <v>0</v>
+      </c>
+      <c r="S227" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO227" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP227" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR227" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS227" t="inlineStr"/>
+      <c r="AT227" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU227" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV227" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE227" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF227" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG227" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH227" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI227" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ227" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
-        </is>
-      </c>
-      <c r="AK227" t="inlineStr">
-        <is>
-          <t>Korea KDCA novel influenza category.</t>
-        </is>
-      </c>
-      <c r="AM227" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN227" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO227" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP227" t="inlineStr">
-        <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ227" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AR227" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS227" t="inlineStr">
-        <is>
-          <t>SER_KR_ANIMAL_INFLUENZA_HUMAN_INFECTION</t>
-        </is>
-      </c>
-      <c r="AT227" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU227" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
-        </is>
-      </c>
-      <c r="AV227" t="inlineStr">
-        <is>
-          <t>kdca_open_api</t>
-        </is>
-      </c>
       <c r="AW227" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX227" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY227" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ227" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA227" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB227" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC227" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -40872,12 +40920,12 @@
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
@@ -40902,7 +40950,7 @@
       </c>
       <c r="L228" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="M228" t="inlineStr">
@@ -40924,68 +40972,87 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U228" t="inlineStr">
+        <is>
+          <t>SER_KR_ANIMAL_INFLUENZA_HUMAN_INFECTION</t>
+        </is>
+      </c>
+      <c r="AA228" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO228" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP228" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ228" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR228" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS228" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS228" t="inlineStr">
+        <is>
+          <t>SER_KR_ANIMAL_INFLUENZA_HUMAN_INFECTION</t>
+        </is>
+      </c>
       <c r="AT228" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU228" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV228" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW228" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX228" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY228" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ228" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA228" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB228" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC228" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -41012,17 +41079,17 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
@@ -41047,7 +41114,7 @@
       </c>
       <c r="L229" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="M229" t="inlineStr">
@@ -41061,21 +41128,98 @@
       <c r="O229" t="n">
         <v>0</v>
       </c>
-      <c r="P229" t="n">
-        <v>0</v>
-      </c>
-      <c r="R229" t="n">
-        <v>0</v>
-      </c>
-      <c r="S229" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+      <c r="U229" t="inlineStr">
+        <is>
+          <t>SER_KR_ANIMAL_INFLUENZA_HUMAN_INFECTION</t>
+        </is>
+      </c>
+      <c r="V229" t="inlineStr">
+        <is>
+          <t>SER_KR_ANIMAL_INFLUENZA_HUMAN_INFECTION</t>
+        </is>
+      </c>
+      <c r="W229" t="inlineStr">
+        <is>
+          <t>SRC_KR_KDCA</t>
+        </is>
+      </c>
+      <c r="X229" t="inlineStr">
+        <is>
+          <t>동물인플루엔자 인체감염증</t>
+        </is>
+      </c>
+      <c r="Y229" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z229" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA229" t="inlineStr">
         <is>
-          <t>weekly</t>
-        </is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB229" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC229" t="inlineStr">
+        <is>
+          <t>country:KR:national</t>
+        </is>
+      </c>
+      <c r="AD229" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE229" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF229" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG229" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH229" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI229" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ229" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK229" t="inlineStr">
+        <is>
+          <t>Korea KDCA animal influenza infection in humans, retained separately from the generic novel influenza category.</t>
+        </is>
+      </c>
+      <c r="AM229" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN229" t="b">
+        <v>1</v>
       </c>
       <c r="AO229" t="inlineStr">
         <is>
@@ -41084,7 +41228,7 @@
       </c>
       <c r="AP229" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ229" t="inlineStr">
@@ -41092,9 +41236,14 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR229" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS229" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_AVIAN_INFLUENZA; SER_SG_HIST_AVIAN_INFLUENZA</t>
+          <t>SER_KR_ANIMAL_INFLUENZA_HUMAN_INFECTION</t>
         </is>
       </c>
       <c r="AT229" t="n">
@@ -41102,47 +41251,47 @@
       </c>
       <c r="AU229" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV229" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW229" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX229" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY229" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ229" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA229" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB229" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC229" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -41174,12 +41323,12 @@
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
@@ -41204,7 +41353,7 @@
       </c>
       <c r="L230" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="M230" t="inlineStr">
@@ -41218,27 +41367,24 @@
       <c r="O230" t="n">
         <v>0</v>
       </c>
-      <c r="P230" t="n">
-        <v>0</v>
-      </c>
       <c r="U230" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_AVIAN_INFLUENZA</t>
+          <t>SER_KR_NOVEL_INFLUENZA</t>
         </is>
       </c>
       <c r="V230" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_AVIAN_INFLUENZA</t>
+          <t>SER_KR_NOVEL_INFLUENZA</t>
         </is>
       </c>
       <c r="W230" t="inlineStr">
         <is>
-          <t>SRC_SG_CDA_WIDB</t>
+          <t>SRC_KR_KDCA</t>
         </is>
       </c>
       <c r="X230" t="inlineStr">
         <is>
-          <t>Avian Influenza</t>
+          <t>신종인플루엔자</t>
         </is>
       </c>
       <c r="Y230" t="inlineStr">
@@ -41248,12 +41394,12 @@
       </c>
       <c r="Z230" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_surveillance</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA230" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AB230" t="inlineStr">
@@ -41263,7 +41409,7 @@
       </c>
       <c r="AC230" t="inlineStr">
         <is>
-          <t>country:SG:national</t>
+          <t>country:KR:national</t>
         </is>
       </c>
       <c r="AD230" t="inlineStr">
@@ -41273,12 +41419,12 @@
       </c>
       <c r="AE230" t="inlineStr">
         <is>
-          <t>narrower</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="AF230" t="inlineStr">
         <is>
-          <t>conditional</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AG230" t="inlineStr">
@@ -41298,12 +41444,12 @@
       </c>
       <c r="AJ230" t="inlineStr">
         <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK230" t="inlineStr">
         <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+          <t>Korea KDCA novel influenza category.</t>
         </is>
       </c>
       <c r="AM230" t="inlineStr">
@@ -41312,7 +41458,7 @@
         </is>
       </c>
       <c r="AN230" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO230" t="inlineStr">
         <is>
@@ -41321,7 +41467,7 @@
       </c>
       <c r="AP230" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ230" t="inlineStr">
@@ -41329,9 +41475,14 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR230" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS230" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_AVIAN_INFLUENZA; SER_SG_HIST_AVIAN_INFLUENZA</t>
+          <t>SER_KR_ANIMAL_INFLUENZA_HUMAN_INFECTION</t>
         </is>
       </c>
       <c r="AT230" t="n">
@@ -41339,45 +41490,1123 @@
       </c>
       <c r="AU230" t="inlineStr">
         <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV230" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW230" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX230" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY230" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ230" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA230" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB230" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC230" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>D016</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>novel-influenza-a</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>Novel influenza A</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>D016</t>
+        </is>
+      </c>
+      <c r="I231" t="inlineStr">
+        <is>
+          <t>Novel influenza A</t>
+        </is>
+      </c>
+      <c r="J231" t="inlineStr">
+        <is>
+          <t>人感染新亚型流感</t>
+        </is>
+      </c>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L231" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M231" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N231" t="n">
+        <v>0</v>
+      </c>
+      <c r="O231" t="n">
+        <v>0</v>
+      </c>
+      <c r="R231" t="n">
+        <v>0</v>
+      </c>
+      <c r="S231" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO231" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP231" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR231" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS231" t="inlineStr"/>
+      <c r="AT231" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU231" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV231" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW231" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX231" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY231" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ231" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA231" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB231" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC231" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>D016</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>novel-influenza-a</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>Novel influenza A</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>D016</t>
+        </is>
+      </c>
+      <c r="I232" t="inlineStr">
+        <is>
+          <t>Novel influenza A</t>
+        </is>
+      </c>
+      <c r="J232" t="inlineStr">
+        <is>
+          <t>人感染新亚型流感</t>
+        </is>
+      </c>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L232" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M232" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N232" t="n">
+        <v>0</v>
+      </c>
+      <c r="O232" t="n">
+        <v>0</v>
+      </c>
+      <c r="P232" t="n">
+        <v>0</v>
+      </c>
+      <c r="R232" t="n">
+        <v>0</v>
+      </c>
+      <c r="S232" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA232" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO232" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP232" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ232" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS232" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_AVIAN_INFLUENZA; SER_SG_HIST_AVIAN_INFLUENZA</t>
+        </is>
+      </c>
+      <c r="AT232" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU232" t="inlineStr">
+        <is>
           <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
-      <c r="AV230" t="inlineStr">
+      <c r="AV232" t="inlineStr">
         <is>
           <t>cda_weekly_bulletin</t>
         </is>
       </c>
-      <c r="AW230" t="inlineStr">
+      <c r="AW232" t="inlineStr">
         <is>
           <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
-      <c r="AX230" t="inlineStr">
+      <c r="AX232" t="inlineStr">
         <is>
           <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
-      <c r="AY230" t="inlineStr">
+      <c r="AY232" t="inlineStr">
         <is>
           <t>official_csv_and_workbook</t>
         </is>
       </c>
-      <c r="AZ230" t="inlineStr">
+      <c r="AZ232" t="inlineStr">
         <is>
           <t>cda_weekly_bulletin</t>
         </is>
       </c>
-      <c r="BA230" t="inlineStr">
+      <c r="BA232" t="inlineStr">
         <is>
           <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
-      <c r="BB230" t="inlineStr">
+      <c r="BB232" t="inlineStr">
         <is>
           <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
-      <c r="BC230" t="inlineStr">
+      <c r="BC232" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>D016</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>novel-influenza-a</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>Novel influenza A</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>D016</t>
+        </is>
+      </c>
+      <c r="I233" t="inlineStr">
+        <is>
+          <t>Novel influenza A</t>
+        </is>
+      </c>
+      <c r="J233" t="inlineStr">
+        <is>
+          <t>人感染新亚型流感</t>
+        </is>
+      </c>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L233" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M233" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N233" t="n">
+        <v>0</v>
+      </c>
+      <c r="O233" t="n">
+        <v>0</v>
+      </c>
+      <c r="P233" t="n">
+        <v>0</v>
+      </c>
+      <c r="U233" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_AVIAN_INFLUENZA</t>
+        </is>
+      </c>
+      <c r="V233" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_AVIAN_INFLUENZA</t>
+        </is>
+      </c>
+      <c r="W233" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X233" t="inlineStr">
+        <is>
+          <t>Avian Influenza</t>
+        </is>
+      </c>
+      <c r="Y233" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z233" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA233" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB233" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC233" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD233" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE233" t="inlineStr">
+        <is>
+          <t>narrower</t>
+        </is>
+      </c>
+      <c r="AF233" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG233" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH233" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI233" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ233" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK233" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM233" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN233" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO233" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP233" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ233" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS233" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_AVIAN_INFLUENZA; SER_SG_HIST_AVIAN_INFLUENZA</t>
+        </is>
+      </c>
+      <c r="AT233" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU233" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV233" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW233" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX233" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY233" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ233" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA233" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB233" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC233" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>D016</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>novel-influenza-a</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>Novel influenza A</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>D016</t>
+        </is>
+      </c>
+      <c r="I234" t="inlineStr">
+        <is>
+          <t>Novel influenza A</t>
+        </is>
+      </c>
+      <c r="J234" t="inlineStr">
+        <is>
+          <t>人感染新亚型流感</t>
+        </is>
+      </c>
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L234" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M234" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N234" t="n">
+        <v>0</v>
+      </c>
+      <c r="O234" t="n">
+        <v>0</v>
+      </c>
+      <c r="R234" t="n">
+        <v>0</v>
+      </c>
+      <c r="S234" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO234" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP234" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR234" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS234" t="inlineStr"/>
+      <c r="AT234" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU234" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV234" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW234" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX234" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY234" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ234" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA234" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB234" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC234" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>D016</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>novel-influenza-a</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>Novel influenza A</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>D016</t>
+        </is>
+      </c>
+      <c r="I235" t="inlineStr">
+        <is>
+          <t>Novel influenza A</t>
+        </is>
+      </c>
+      <c r="J235" t="inlineStr">
+        <is>
+          <t>人感染新亚型流感</t>
+        </is>
+      </c>
+      <c r="K235" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L235" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M235" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N235" t="n">
+        <v>0</v>
+      </c>
+      <c r="O235" t="n">
+        <v>0</v>
+      </c>
+      <c r="P235" t="n">
+        <v>0</v>
+      </c>
+      <c r="R235" t="n">
+        <v>0</v>
+      </c>
+      <c r="S235" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA235" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO235" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP235" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ235" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS235" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_AVIAN_INFLUENZA; SER_SG_HIST_AVIAN_INFLUENZA</t>
+        </is>
+      </c>
+      <c r="AT235" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU235" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV235" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW235" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX235" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY235" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ235" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA235" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB235" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC235" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>D016</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>novel-influenza-a</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>Novel influenza A</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H236" t="inlineStr">
+        <is>
+          <t>D016</t>
+        </is>
+      </c>
+      <c r="I236" t="inlineStr">
+        <is>
+          <t>Novel influenza A</t>
+        </is>
+      </c>
+      <c r="J236" t="inlineStr">
+        <is>
+          <t>人感染新亚型流感</t>
+        </is>
+      </c>
+      <c r="K236" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L236" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M236" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N236" t="n">
+        <v>0</v>
+      </c>
+      <c r="O236" t="n">
+        <v>0</v>
+      </c>
+      <c r="P236" t="n">
+        <v>0</v>
+      </c>
+      <c r="U236" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_AVIAN_INFLUENZA</t>
+        </is>
+      </c>
+      <c r="V236" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_AVIAN_INFLUENZA</t>
+        </is>
+      </c>
+      <c r="W236" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X236" t="inlineStr">
+        <is>
+          <t>Avian Influenza</t>
+        </is>
+      </c>
+      <c r="Y236" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z236" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA236" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB236" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC236" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD236" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE236" t="inlineStr">
+        <is>
+          <t>narrower</t>
+        </is>
+      </c>
+      <c r="AF236" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG236" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH236" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI236" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ236" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK236" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM236" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN236" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO236" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP236" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ236" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS236" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_AVIAN_INFLUENZA; SER_SG_HIST_AVIAN_INFLUENZA</t>
+        </is>
+      </c>
+      <c r="AT236" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU236" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV236" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW236" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX236" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY236" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ236" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA236" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB236" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC236" t="inlineStr">
         <is>
           <t>official_csv_and_workbook</t>
         </is>
@@ -41416,7 +42645,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -41499,7 +42728,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="10">
@@ -41509,7 +42738,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>229</v>
+        <v>235</v>
       </c>
     </row>
     <row r="11">
@@ -41529,7 +42758,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>75</v>
+        <v>79</v>
       </c>
     </row>
     <row r="13">

--- a/diseases/d016/2026-2029.xlsx
+++ b/diseases/d016/2026-2029.xlsx
@@ -53532,6 +53532,1187 @@
         </is>
       </c>
     </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>D016</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>novel-influenza-a</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>Novel influenza A</t>
+        </is>
+      </c>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F293" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G293" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H293" t="inlineStr">
+        <is>
+          <t>D016</t>
+        </is>
+      </c>
+      <c r="I293" t="inlineStr">
+        <is>
+          <t>Novel influenza A</t>
+        </is>
+      </c>
+      <c r="J293" t="inlineStr">
+        <is>
+          <t>人感染新亚型流感</t>
+        </is>
+      </c>
+      <c r="K293" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L293" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="M293" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N293" t="n">
+        <v>0</v>
+      </c>
+      <c r="O293" t="n">
+        <v>0</v>
+      </c>
+      <c r="R293" t="n">
+        <v>0</v>
+      </c>
+      <c r="S293" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO293" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP293" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR293" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS293" t="inlineStr"/>
+      <c r="AT293" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU293" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV293" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW293" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX293" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY293" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ293" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA293" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB293" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC293" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>D016</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>novel-influenza-a</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>Novel influenza A</t>
+        </is>
+      </c>
+      <c r="E294" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F294" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G294" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H294" t="inlineStr">
+        <is>
+          <t>D016</t>
+        </is>
+      </c>
+      <c r="I294" t="inlineStr">
+        <is>
+          <t>Novel influenza A</t>
+        </is>
+      </c>
+      <c r="J294" t="inlineStr">
+        <is>
+          <t>人感染新亚型流感</t>
+        </is>
+      </c>
+      <c r="K294" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L294" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="M294" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N294" t="n">
+        <v>0</v>
+      </c>
+      <c r="O294" t="n">
+        <v>0</v>
+      </c>
+      <c r="P294" t="n">
+        <v>0</v>
+      </c>
+      <c r="R294" t="n">
+        <v>0</v>
+      </c>
+      <c r="S294" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA294" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO294" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP294" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ294" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS294" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_AVIAN_INFLUENZA; SER_SG_HIST_AVIAN_INFLUENZA</t>
+        </is>
+      </c>
+      <c r="AT294" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU294" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV294" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW294" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX294" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY294" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ294" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA294" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB294" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC294" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>D016</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>novel-influenza-a</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>Novel influenza A</t>
+        </is>
+      </c>
+      <c r="E295" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F295" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G295" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H295" t="inlineStr">
+        <is>
+          <t>D016</t>
+        </is>
+      </c>
+      <c r="I295" t="inlineStr">
+        <is>
+          <t>Novel influenza A</t>
+        </is>
+      </c>
+      <c r="J295" t="inlineStr">
+        <is>
+          <t>人感染新亚型流感</t>
+        </is>
+      </c>
+      <c r="K295" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L295" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="M295" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N295" t="n">
+        <v>0</v>
+      </c>
+      <c r="O295" t="n">
+        <v>0</v>
+      </c>
+      <c r="P295" t="n">
+        <v>0</v>
+      </c>
+      <c r="U295" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_AVIAN_INFLUENZA</t>
+        </is>
+      </c>
+      <c r="V295" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_AVIAN_INFLUENZA</t>
+        </is>
+      </c>
+      <c r="W295" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X295" t="inlineStr">
+        <is>
+          <t>Avian Influenza</t>
+        </is>
+      </c>
+      <c r="Y295" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z295" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA295" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB295" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC295" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD295" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE295" t="inlineStr">
+        <is>
+          <t>narrower</t>
+        </is>
+      </c>
+      <c r="AF295" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG295" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH295" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI295" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ295" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK295" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM295" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN295" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO295" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP295" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ295" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS295" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_AVIAN_INFLUENZA; SER_SG_HIST_AVIAN_INFLUENZA</t>
+        </is>
+      </c>
+      <c r="AT295" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU295" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV295" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW295" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX295" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY295" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ295" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA295" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB295" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC295" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>D016</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>novel-influenza-a</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>Novel influenza A</t>
+        </is>
+      </c>
+      <c r="E296" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F296" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G296" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H296" t="inlineStr">
+        <is>
+          <t>D016</t>
+        </is>
+      </c>
+      <c r="I296" t="inlineStr">
+        <is>
+          <t>Novel influenza A</t>
+        </is>
+      </c>
+      <c r="J296" t="inlineStr">
+        <is>
+          <t>人感染新亚型流感</t>
+        </is>
+      </c>
+      <c r="K296" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L296" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M296" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N296" t="n">
+        <v>0</v>
+      </c>
+      <c r="O296" t="n">
+        <v>0</v>
+      </c>
+      <c r="R296" t="n">
+        <v>0</v>
+      </c>
+      <c r="S296" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U296" t="inlineStr">
+        <is>
+          <t>SER_KR_ANIMAL_INFLUENZA_HUMAN_INFECTION</t>
+        </is>
+      </c>
+      <c r="AA296" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO296" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP296" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ296" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR296" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS296" t="inlineStr">
+        <is>
+          <t>SER_KR_ANIMAL_INFLUENZA_HUMAN_INFECTION</t>
+        </is>
+      </c>
+      <c r="AT296" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU296" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV296" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW296" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX296" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY296" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ296" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA296" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB296" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC296" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>D016</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>novel-influenza-a</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>Novel influenza A</t>
+        </is>
+      </c>
+      <c r="E297" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F297" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G297" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H297" t="inlineStr">
+        <is>
+          <t>D016</t>
+        </is>
+      </c>
+      <c r="I297" t="inlineStr">
+        <is>
+          <t>Novel influenza A</t>
+        </is>
+      </c>
+      <c r="J297" t="inlineStr">
+        <is>
+          <t>人感染新亚型流感</t>
+        </is>
+      </c>
+      <c r="K297" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L297" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M297" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N297" t="n">
+        <v>0</v>
+      </c>
+      <c r="O297" t="n">
+        <v>0</v>
+      </c>
+      <c r="U297" t="inlineStr">
+        <is>
+          <t>SER_KR_ANIMAL_INFLUENZA_HUMAN_INFECTION</t>
+        </is>
+      </c>
+      <c r="V297" t="inlineStr">
+        <is>
+          <t>SER_KR_ANIMAL_INFLUENZA_HUMAN_INFECTION</t>
+        </is>
+      </c>
+      <c r="W297" t="inlineStr">
+        <is>
+          <t>SRC_KR_KDCA</t>
+        </is>
+      </c>
+      <c r="X297" t="inlineStr">
+        <is>
+          <t>동물인플루엔자 인체감염증</t>
+        </is>
+      </c>
+      <c r="Y297" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z297" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA297" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB297" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC297" t="inlineStr">
+        <is>
+          <t>country:KR:national</t>
+        </is>
+      </c>
+      <c r="AD297" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE297" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF297" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG297" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH297" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI297" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ297" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK297" t="inlineStr">
+        <is>
+          <t>Korea KDCA animal influenza infection in humans, retained separately from the generic novel influenza category.</t>
+        </is>
+      </c>
+      <c r="AM297" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN297" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO297" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP297" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ297" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR297" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS297" t="inlineStr">
+        <is>
+          <t>SER_KR_ANIMAL_INFLUENZA_HUMAN_INFECTION</t>
+        </is>
+      </c>
+      <c r="AT297" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU297" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV297" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW297" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX297" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY297" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ297" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA297" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB297" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC297" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>D016</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>novel-influenza-a</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>Novel influenza A</t>
+        </is>
+      </c>
+      <c r="E298" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F298" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G298" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H298" t="inlineStr">
+        <is>
+          <t>D016</t>
+        </is>
+      </c>
+      <c r="I298" t="inlineStr">
+        <is>
+          <t>Novel influenza A</t>
+        </is>
+      </c>
+      <c r="J298" t="inlineStr">
+        <is>
+          <t>人感染新亚型流感</t>
+        </is>
+      </c>
+      <c r="K298" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L298" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M298" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N298" t="n">
+        <v>0</v>
+      </c>
+      <c r="O298" t="n">
+        <v>0</v>
+      </c>
+      <c r="U298" t="inlineStr">
+        <is>
+          <t>SER_KR_NOVEL_INFLUENZA</t>
+        </is>
+      </c>
+      <c r="V298" t="inlineStr">
+        <is>
+          <t>SER_KR_NOVEL_INFLUENZA</t>
+        </is>
+      </c>
+      <c r="W298" t="inlineStr">
+        <is>
+          <t>SRC_KR_KDCA</t>
+        </is>
+      </c>
+      <c r="X298" t="inlineStr">
+        <is>
+          <t>신종인플루엔자</t>
+        </is>
+      </c>
+      <c r="Y298" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z298" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA298" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB298" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC298" t="inlineStr">
+        <is>
+          <t>country:KR:national</t>
+        </is>
+      </c>
+      <c r="AD298" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE298" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF298" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG298" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH298" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI298" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ298" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK298" t="inlineStr">
+        <is>
+          <t>Korea KDCA novel influenza category.</t>
+        </is>
+      </c>
+      <c r="AM298" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN298" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO298" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP298" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ298" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR298" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS298" t="inlineStr">
+        <is>
+          <t>SER_KR_ANIMAL_INFLUENZA_HUMAN_INFECTION</t>
+        </is>
+      </c>
+      <c r="AT298" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU298" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV298" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW298" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX298" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY298" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ298" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA298" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB298" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC298" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -53565,7 +54746,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-10-01</t>
         </is>
       </c>
     </row>
@@ -53648,7 +54829,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>184</v>
+        <v>187</v>
       </c>
     </row>
     <row r="10">
@@ -53658,7 +54839,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>291</v>
+        <v>297</v>
       </c>
     </row>
     <row r="11">
@@ -53678,7 +54859,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>107</v>
+        <v>110</v>
       </c>
     </row>
     <row r="13">

--- a/diseases/d016/2026-2029.xlsx
+++ b/diseases/d016/2026-2029.xlsx
@@ -776,6 +776,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO2" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -921,6 +926,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO3" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1066,6 +1076,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO4" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1211,6 +1226,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO5" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1356,6 +1376,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO6" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1501,6 +1526,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO7" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1646,6 +1676,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO8" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1791,6 +1826,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO9" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1936,6 +1976,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO10" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2084,6 +2129,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO11" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3954,6 +4004,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO20" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4644,6 +4699,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO24" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5334,6 +5394,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO28" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6024,6 +6089,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO32" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6714,6 +6784,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO36" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6862,6 +6937,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO37" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7007,6 +7087,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO38" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7152,6 +7237,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO39" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7297,6 +7387,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO40" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7442,6 +7537,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO41" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7587,6 +7687,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO42" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7732,6 +7837,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO43" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7877,6 +7987,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO44" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8022,6 +8137,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO45" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8170,6 +8290,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO46" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10582,6 +10707,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO58" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11272,6 +11402,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO62" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11962,6 +12097,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO66" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12652,6 +12792,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO70" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12800,6 +12945,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO71" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12945,6 +13095,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO72" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13090,6 +13245,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO73" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13235,6 +13395,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO74" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13380,6 +13545,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO75" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13525,6 +13695,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO76" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13670,6 +13845,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO77" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13815,6 +13995,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO78" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13960,6 +14145,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO79" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14108,6 +14298,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO80" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16278,6 +16473,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO91" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16968,6 +17168,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO95" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17658,6 +17863,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO99" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18348,6 +18558,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO103" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18887,6 +19102,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO106" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19032,6 +19252,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO107" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19177,6 +19402,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO108" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19322,6 +19552,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO109" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19467,6 +19702,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO110" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19612,6 +19852,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA111" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO111" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19757,6 +20002,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO112" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19902,6 +20152,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO113" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20047,6 +20302,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA114" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO114" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20195,6 +20455,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA115" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO115" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21823,6 +22088,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA123" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO123" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22513,6 +22783,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA127" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO127" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23203,6 +23478,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA131" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO131" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23893,6 +24173,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA135" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO135" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24432,6 +24717,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA138" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO138" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24577,6 +24867,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA139" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO139" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24722,6 +25017,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA140" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO140" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24867,6 +25167,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA141" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO141" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25012,6 +25317,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA142" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO142" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25157,6 +25467,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA143" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO143" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25302,6 +25617,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA144" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO144" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25447,6 +25767,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA145" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO145" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25592,6 +25917,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA146" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO146" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25740,6 +26070,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA147" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO147" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28148,6 +28483,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA159" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO159" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28838,6 +29178,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA163" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO163" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29528,6 +29873,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA167" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO167" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30218,6 +30568,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA171" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO171" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30908,6 +31263,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA175" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO175" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31447,6 +31807,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA178" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO178" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31592,6 +31957,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA179" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO179" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31737,6 +32107,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA180" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO180" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31882,6 +32257,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA181" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO181" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32027,6 +32407,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA182" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO182" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32172,6 +32557,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA183" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO183" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32317,6 +32707,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA184" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO184" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32462,6 +32857,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA185" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO185" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32607,6 +33007,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA186" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO186" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32755,6 +33160,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA187" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO187" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -37497,6 +37907,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA211" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO211" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -38181,6 +38596,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA215" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO215" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -38865,6 +39285,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA219" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO219" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -39549,6 +39974,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA223" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO223" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -40088,6 +40518,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA226" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO226" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -40233,6 +40668,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA227" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO227" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -40378,6 +40818,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA228" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO228" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -40523,6 +40968,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA229" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO229" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -40668,6 +41118,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA230" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO230" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -40813,6 +41268,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA231" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO231" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -40958,6 +41418,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA232" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO232" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -41103,6 +41568,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA233" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO233" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -41248,6 +41718,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA234" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO234" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -41396,6 +41871,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA235" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO235" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -46528,6 +47008,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA261" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO261" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -47212,6 +47697,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA265" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO265" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -47896,6 +48386,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA269" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO269" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -48580,6 +49075,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA273" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO273" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -49264,6 +49764,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA277" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO277" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -49409,6 +49914,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA278" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO278" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -49554,6 +50064,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA279" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO279" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -49699,6 +50214,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA280" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO280" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -49844,6 +50364,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA281" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO281" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -49989,6 +50514,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA282" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO282" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -50134,6 +50664,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA283" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO283" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -50279,6 +50814,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA284" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO284" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -50424,6 +50964,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA285" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO285" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -50572,6 +51117,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA286" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO286" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -56396,6 +56946,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA316" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO316" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -57619,6 +58174,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA323" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO323" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -57764,6 +58324,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA324" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO324" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -57909,6 +58474,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA325" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO325" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -58054,6 +58624,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA326" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO326" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -58199,6 +58774,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA327" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO327" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -58344,6 +58924,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA328" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO328" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -58489,6 +59074,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA329" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO329" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -58634,6 +59224,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA330" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO330" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -58779,6 +59374,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA331" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO331" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -61276,12 +61876,12 @@
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G345" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H345" t="inlineStr">
@@ -61306,12 +61906,12 @@
       </c>
       <c r="L345" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="M345" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="N345" t="n">
@@ -61320,6 +61920,9 @@
       <c r="O345" t="n">
         <v>0</v>
       </c>
+      <c r="P345" t="n">
+        <v>0</v>
+      </c>
       <c r="R345" t="n">
         <v>0</v>
       </c>
@@ -61328,14 +61931,9 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U345" t="inlineStr">
-        <is>
-          <t>SER_KR_ANIMAL_INFLUENZA_HUMAN_INFECTION</t>
-        </is>
-      </c>
       <c r="AA345" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO345" t="inlineStr">
@@ -61345,7 +61943,7 @@
       </c>
       <c r="AP345" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>temporal_handoff</t>
         </is>
       </c>
       <c r="AQ345" t="inlineStr">
@@ -61353,14 +61951,9 @@
           <t>parity</t>
         </is>
       </c>
-      <c r="AR345" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
       <c r="AS345" t="inlineStr">
         <is>
-          <t>SER_KR_ANIMAL_INFLUENZA_HUMAN_INFECTION</t>
+          <t>SER_SG_CDA_AVIAN_INFLUENZA; SER_SG_HIST_AVIAN_INFLUENZA</t>
         </is>
       </c>
       <c r="AT345" t="n">
@@ -61368,47 +61961,47 @@
       </c>
       <c r="AU345" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV345" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW345" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX345" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY345" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ345" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA345" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB345" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC345" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -61440,12 +62033,12 @@
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G346" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H346" t="inlineStr">
@@ -61470,12 +62063,12 @@
       </c>
       <c r="L346" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="M346" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="N346" t="n">
@@ -61484,24 +62077,27 @@
       <c r="O346" t="n">
         <v>0</v>
       </c>
+      <c r="P346" t="n">
+        <v>0</v>
+      </c>
       <c r="U346" t="inlineStr">
         <is>
-          <t>SER_KR_ANIMAL_INFLUENZA_HUMAN_INFECTION</t>
+          <t>SER_SG_CDA_AVIAN_INFLUENZA</t>
         </is>
       </c>
       <c r="V346" t="inlineStr">
         <is>
-          <t>SER_KR_ANIMAL_INFLUENZA_HUMAN_INFECTION</t>
+          <t>SER_SG_CDA_AVIAN_INFLUENZA</t>
         </is>
       </c>
       <c r="W346" t="inlineStr">
         <is>
-          <t>SRC_KR_KDCA</t>
+          <t>SRC_SG_CDA_WIDB</t>
         </is>
       </c>
       <c r="X346" t="inlineStr">
         <is>
-          <t>동물인플루엔자 인체감염증</t>
+          <t>Avian Influenza</t>
         </is>
       </c>
       <c r="Y346" t="inlineStr">
@@ -61511,12 +62107,12 @@
       </c>
       <c r="Z346" t="inlineStr">
         <is>
-          <t>notification</t>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA346" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AB346" t="inlineStr">
@@ -61526,7 +62122,7 @@
       </c>
       <c r="AC346" t="inlineStr">
         <is>
-          <t>country:KR:national</t>
+          <t>country:SG:national</t>
         </is>
       </c>
       <c r="AD346" t="inlineStr">
@@ -61536,12 +62132,12 @@
       </c>
       <c r="AE346" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>narrower</t>
         </is>
       </c>
       <c r="AF346" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>conditional</t>
         </is>
       </c>
       <c r="AG346" t="inlineStr">
@@ -61561,12 +62157,12 @@
       </c>
       <c r="AJ346" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
         </is>
       </c>
       <c r="AK346" t="inlineStr">
         <is>
-          <t>Korea KDCA animal influenza infection in humans, retained separately from the generic novel influenza category.</t>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
         </is>
       </c>
       <c r="AM346" t="inlineStr">
@@ -61584,7 +62180,7 @@
       </c>
       <c r="AP346" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>temporal_handoff</t>
         </is>
       </c>
       <c r="AQ346" t="inlineStr">
@@ -61592,14 +62188,9 @@
           <t>parity</t>
         </is>
       </c>
-      <c r="AR346" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
       <c r="AS346" t="inlineStr">
         <is>
-          <t>SER_KR_ANIMAL_INFLUENZA_HUMAN_INFECTION</t>
+          <t>SER_SG_CDA_AVIAN_INFLUENZA; SER_SG_HIST_AVIAN_INFLUENZA</t>
         </is>
       </c>
       <c r="AT346" t="n">
@@ -61607,47 +62198,47 @@
       </c>
       <c r="AU346" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV346" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW346" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX346" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY346" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ346" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA346" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB346" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC346" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -61674,7 +62265,7 @@
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F347" t="inlineStr">
@@ -61723,98 +62314,23 @@
       <c r="O347" t="n">
         <v>0</v>
       </c>
+      <c r="R347" t="n">
+        <v>0</v>
+      </c>
+      <c r="S347" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U347" t="inlineStr">
         <is>
-          <t>SER_KR_NOVEL_INFLUENZA</t>
-        </is>
-      </c>
-      <c r="V347" t="inlineStr">
-        <is>
-          <t>SER_KR_NOVEL_INFLUENZA</t>
-        </is>
-      </c>
-      <c r="W347" t="inlineStr">
-        <is>
-          <t>SRC_KR_KDCA</t>
-        </is>
-      </c>
-      <c r="X347" t="inlineStr">
-        <is>
-          <t>신종인플루엔자</t>
-        </is>
-      </c>
-      <c r="Y347" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z347" t="inlineStr">
-        <is>
-          <t>notification</t>
+          <t>SER_KR_ANIMAL_INFLUENZA_HUMAN_INFECTION</t>
         </is>
       </c>
       <c r="AA347" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB347" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC347" t="inlineStr">
-        <is>
-          <t>country:KR:national</t>
-        </is>
-      </c>
-      <c r="AD347" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE347" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF347" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG347" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH347" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI347" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ347" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
-        </is>
-      </c>
-      <c r="AK347" t="inlineStr">
-        <is>
-          <t>Korea KDCA novel influenza category.</t>
-        </is>
-      </c>
-      <c r="AM347" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN347" t="b">
-        <v>0</v>
       </c>
       <c r="AO347" t="inlineStr">
         <is>
@@ -61885,6 +62401,484 @@
         </is>
       </c>
       <c r="BC347" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>D016</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>novel-influenza-a</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>Novel influenza A</t>
+        </is>
+      </c>
+      <c r="E348" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F348" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G348" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H348" t="inlineStr">
+        <is>
+          <t>D016</t>
+        </is>
+      </c>
+      <c r="I348" t="inlineStr">
+        <is>
+          <t>Novel influenza A</t>
+        </is>
+      </c>
+      <c r="J348" t="inlineStr">
+        <is>
+          <t>人感染新亚型流感</t>
+        </is>
+      </c>
+      <c r="K348" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L348" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M348" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N348" t="n">
+        <v>0</v>
+      </c>
+      <c r="O348" t="n">
+        <v>0</v>
+      </c>
+      <c r="U348" t="inlineStr">
+        <is>
+          <t>SER_KR_ANIMAL_INFLUENZA_HUMAN_INFECTION</t>
+        </is>
+      </c>
+      <c r="V348" t="inlineStr">
+        <is>
+          <t>SER_KR_ANIMAL_INFLUENZA_HUMAN_INFECTION</t>
+        </is>
+      </c>
+      <c r="W348" t="inlineStr">
+        <is>
+          <t>SRC_KR_KDCA</t>
+        </is>
+      </c>
+      <c r="X348" t="inlineStr">
+        <is>
+          <t>동물인플루엔자 인체감염증</t>
+        </is>
+      </c>
+      <c r="Y348" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z348" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA348" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB348" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC348" t="inlineStr">
+        <is>
+          <t>country:KR:national</t>
+        </is>
+      </c>
+      <c r="AD348" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE348" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF348" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG348" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH348" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI348" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ348" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK348" t="inlineStr">
+        <is>
+          <t>Korea KDCA animal influenza infection in humans, retained separately from the generic novel influenza category.</t>
+        </is>
+      </c>
+      <c r="AM348" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN348" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO348" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP348" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ348" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR348" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS348" t="inlineStr">
+        <is>
+          <t>SER_KR_ANIMAL_INFLUENZA_HUMAN_INFECTION</t>
+        </is>
+      </c>
+      <c r="AT348" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU348" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV348" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW348" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX348" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY348" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ348" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA348" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB348" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC348" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>D016</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>novel-influenza-a</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>Novel influenza A</t>
+        </is>
+      </c>
+      <c r="E349" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F349" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G349" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H349" t="inlineStr">
+        <is>
+          <t>D016</t>
+        </is>
+      </c>
+      <c r="I349" t="inlineStr">
+        <is>
+          <t>Novel influenza A</t>
+        </is>
+      </c>
+      <c r="J349" t="inlineStr">
+        <is>
+          <t>人感染新亚型流感</t>
+        </is>
+      </c>
+      <c r="K349" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L349" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M349" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N349" t="n">
+        <v>0</v>
+      </c>
+      <c r="O349" t="n">
+        <v>0</v>
+      </c>
+      <c r="U349" t="inlineStr">
+        <is>
+          <t>SER_KR_NOVEL_INFLUENZA</t>
+        </is>
+      </c>
+      <c r="V349" t="inlineStr">
+        <is>
+          <t>SER_KR_NOVEL_INFLUENZA</t>
+        </is>
+      </c>
+      <c r="W349" t="inlineStr">
+        <is>
+          <t>SRC_KR_KDCA</t>
+        </is>
+      </c>
+      <c r="X349" t="inlineStr">
+        <is>
+          <t>신종인플루엔자</t>
+        </is>
+      </c>
+      <c r="Y349" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z349" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA349" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB349" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC349" t="inlineStr">
+        <is>
+          <t>country:KR:national</t>
+        </is>
+      </c>
+      <c r="AD349" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE349" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF349" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG349" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH349" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI349" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ349" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK349" t="inlineStr">
+        <is>
+          <t>Korea KDCA novel influenza category.</t>
+        </is>
+      </c>
+      <c r="AM349" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN349" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO349" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP349" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ349" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR349" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS349" t="inlineStr">
+        <is>
+          <t>SER_KR_ANIMAL_INFLUENZA_HUMAN_INFECTION</t>
+        </is>
+      </c>
+      <c r="AT349" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU349" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV349" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW349" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX349" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY349" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ349" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA349" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB349" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC349" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
@@ -62006,7 +63000,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="10">
@@ -62016,7 +63010,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row r="11">
@@ -62036,7 +63030,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="13">

--- a/diseases/d016/2026-2029.xlsx
+++ b/diseases/d016/2026-2029.xlsx
@@ -62884,6 +62884,151 @@
         </is>
       </c>
     </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>D016</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>novel-influenza-a</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>Novel influenza A</t>
+        </is>
+      </c>
+      <c r="E350" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F350" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G350" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H350" t="inlineStr">
+        <is>
+          <t>D016</t>
+        </is>
+      </c>
+      <c r="I350" t="inlineStr">
+        <is>
+          <t>Novel influenza A</t>
+        </is>
+      </c>
+      <c r="J350" t="inlineStr">
+        <is>
+          <t>人感染新亚型流感</t>
+        </is>
+      </c>
+      <c r="K350" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L350" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="M350" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N350" t="n">
+        <v>0</v>
+      </c>
+      <c r="O350" t="n">
+        <v>0</v>
+      </c>
+      <c r="R350" t="n">
+        <v>0</v>
+      </c>
+      <c r="S350" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO350" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP350" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR350" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS350" t="inlineStr"/>
+      <c r="AT350" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU350" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV350" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW350" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX350" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY350" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ350" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA350" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB350" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC350" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -62917,7 +63062,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -63000,7 +63145,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="10">
@@ -63010,7 +63155,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="11">

--- a/diseases/d016/2026-2029.xlsx
+++ b/diseases/d016/2026-2029.xlsx
@@ -3592,7 +3592,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
@@ -3831,7 +3831,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -3993,6 +3993,9 @@
       <c r="O20" t="n">
         <v>0</v>
       </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
@@ -4004,6 +4007,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>HOLD_US_25a3245e6faa66bb52d11f87954b</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -4011,26 +4019,35 @@
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ20" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS20" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS20" t="inlineStr">
+        <is>
+          <t>HOLD_US_25a3245e6faa66bb52d11f87954b</t>
+        </is>
+      </c>
       <c r="AT20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AU20" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV20" t="inlineStr">
@@ -4688,6 +4705,9 @@
       <c r="O24" t="n">
         <v>0</v>
       </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
       <c r="Q24" t="n">
         <v>0</v>
       </c>
@@ -4699,6 +4719,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>HOLD_US_25a3245e6faa66bb52d11f87954b</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -4706,26 +4731,35 @@
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP24" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ24" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AR24" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS24" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS24" t="inlineStr">
+        <is>
+          <t>HOLD_US_25a3245e6faa66bb52d11f87954b</t>
+        </is>
+      </c>
       <c r="AT24" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AU24" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV24" t="inlineStr">
@@ -5383,6 +5417,9 @@
       <c r="O28" t="n">
         <v>0</v>
       </c>
+      <c r="P28" t="n">
+        <v>0</v>
+      </c>
       <c r="Q28" t="n">
         <v>0</v>
       </c>
@@ -5394,6 +5431,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>HOLD_US_25a3245e6faa66bb52d11f87954b</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -5401,26 +5443,35 @@
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP28" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ28" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AR28" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS28" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS28" t="inlineStr">
+        <is>
+          <t>HOLD_US_25a3245e6faa66bb52d11f87954b</t>
+        </is>
+      </c>
       <c r="AT28" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AU28" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV28" t="inlineStr">
@@ -6078,6 +6129,9 @@
       <c r="O32" t="n">
         <v>0</v>
       </c>
+      <c r="P32" t="n">
+        <v>0</v>
+      </c>
       <c r="Q32" t="n">
         <v>0</v>
       </c>
@@ -6089,6 +6143,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>HOLD_US_25a3245e6faa66bb52d11f87954b</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -6096,26 +6155,35 @@
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP32" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ32" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AR32" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS32" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS32" t="inlineStr">
+        <is>
+          <t>HOLD_US_25a3245e6faa66bb52d11f87954b</t>
+        </is>
+      </c>
       <c r="AT32" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AU32" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV32" t="inlineStr">
@@ -6773,6 +6841,9 @@
       <c r="O36" t="n">
         <v>0</v>
       </c>
+      <c r="P36" t="n">
+        <v>0</v>
+      </c>
       <c r="Q36" t="n">
         <v>0</v>
       </c>
@@ -6784,6 +6855,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>HOLD_US_25a3245e6faa66bb52d11f87954b</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -6791,26 +6867,35 @@
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP36" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ36" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AR36" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS36" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS36" t="inlineStr">
+        <is>
+          <t>HOLD_US_25a3245e6faa66bb52d11f87954b</t>
+        </is>
+      </c>
       <c r="AT36" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AU36" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV36" t="inlineStr">
@@ -9753,7 +9838,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -9992,7 +10077,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK54" t="inlineStr">
@@ -10696,6 +10781,9 @@
       <c r="O58" t="n">
         <v>0</v>
       </c>
+      <c r="P58" t="n">
+        <v>0</v>
+      </c>
       <c r="Q58" t="n">
         <v>0</v>
       </c>
@@ -10707,6 +10795,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>HOLD_US_25a3245e6faa66bb52d11f87954b</t>
+        </is>
+      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -10714,26 +10807,35 @@
       </c>
       <c r="AO58" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP58" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ58" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AR58" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS58" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS58" t="inlineStr">
+        <is>
+          <t>HOLD_US_25a3245e6faa66bb52d11f87954b</t>
+        </is>
+      </c>
       <c r="AT58" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AU58" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV58" t="inlineStr">
@@ -11391,6 +11493,9 @@
       <c r="O62" t="n">
         <v>0</v>
       </c>
+      <c r="P62" t="n">
+        <v>0</v>
+      </c>
       <c r="Q62" t="n">
         <v>0</v>
       </c>
@@ -11402,6 +11507,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>HOLD_US_25a3245e6faa66bb52d11f87954b</t>
+        </is>
+      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -11409,26 +11519,35 @@
       </c>
       <c r="AO62" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP62" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ62" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AR62" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS62" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS62" t="inlineStr">
+        <is>
+          <t>HOLD_US_25a3245e6faa66bb52d11f87954b</t>
+        </is>
+      </c>
       <c r="AT62" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AU62" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV62" t="inlineStr">
@@ -12086,6 +12205,9 @@
       <c r="O66" t="n">
         <v>0</v>
       </c>
+      <c r="P66" t="n">
+        <v>0</v>
+      </c>
       <c r="Q66" t="n">
         <v>0</v>
       </c>
@@ -12097,6 +12219,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>HOLD_US_25a3245e6faa66bb52d11f87954b</t>
+        </is>
+      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -12104,26 +12231,35 @@
       </c>
       <c r="AO66" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP66" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ66" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AR66" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS66" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS66" t="inlineStr">
+        <is>
+          <t>HOLD_US_25a3245e6faa66bb52d11f87954b</t>
+        </is>
+      </c>
       <c r="AT66" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AU66" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV66" t="inlineStr">
@@ -12781,6 +12917,9 @@
       <c r="O70" t="n">
         <v>0</v>
       </c>
+      <c r="P70" t="n">
+        <v>0</v>
+      </c>
       <c r="Q70" t="n">
         <v>0</v>
       </c>
@@ -12792,6 +12931,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>HOLD_US_25a3245e6faa66bb52d11f87954b</t>
+        </is>
+      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -12799,26 +12943,35 @@
       </c>
       <c r="AO70" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP70" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ70" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AR70" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS70" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS70" t="inlineStr">
+        <is>
+          <t>HOLD_US_25a3245e6faa66bb52d11f87954b</t>
+        </is>
+      </c>
       <c r="AT70" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AU70" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV70" t="inlineStr">
@@ -15371,7 +15524,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -15610,7 +15763,7 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK86" t="inlineStr">
@@ -16462,6 +16615,9 @@
       <c r="O91" t="n">
         <v>0</v>
       </c>
+      <c r="P91" t="n">
+        <v>0</v>
+      </c>
       <c r="Q91" t="n">
         <v>0</v>
       </c>
@@ -16473,6 +16629,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>HOLD_US_25a3245e6faa66bb52d11f87954b</t>
+        </is>
+      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -16480,26 +16641,35 @@
       </c>
       <c r="AO91" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP91" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ91" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AR91" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS91" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS91" t="inlineStr">
+        <is>
+          <t>HOLD_US_25a3245e6faa66bb52d11f87954b</t>
+        </is>
+      </c>
       <c r="AT91" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AU91" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV91" t="inlineStr">
@@ -17157,6 +17327,9 @@
       <c r="O95" t="n">
         <v>0</v>
       </c>
+      <c r="P95" t="n">
+        <v>0</v>
+      </c>
       <c r="Q95" t="n">
         <v>0</v>
       </c>
@@ -17168,6 +17341,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>HOLD_US_25a3245e6faa66bb52d11f87954b</t>
+        </is>
+      </c>
       <c r="AA95" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -17175,26 +17353,35 @@
       </c>
       <c r="AO95" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP95" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ95" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AR95" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS95" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS95" t="inlineStr">
+        <is>
+          <t>HOLD_US_25a3245e6faa66bb52d11f87954b</t>
+        </is>
+      </c>
       <c r="AT95" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AU95" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV95" t="inlineStr">
@@ -17852,6 +18039,9 @@
       <c r="O99" t="n">
         <v>0</v>
       </c>
+      <c r="P99" t="n">
+        <v>0</v>
+      </c>
       <c r="Q99" t="n">
         <v>0</v>
       </c>
@@ -17863,6 +18053,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>HOLD_US_25a3245e6faa66bb52d11f87954b</t>
+        </is>
+      </c>
       <c r="AA99" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -17870,26 +18065,35 @@
       </c>
       <c r="AO99" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP99" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ99" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AR99" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS99" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS99" t="inlineStr">
+        <is>
+          <t>HOLD_US_25a3245e6faa66bb52d11f87954b</t>
+        </is>
+      </c>
       <c r="AT99" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AU99" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV99" t="inlineStr">
@@ -18547,6 +18751,9 @@
       <c r="O103" t="n">
         <v>0</v>
       </c>
+      <c r="P103" t="n">
+        <v>0</v>
+      </c>
       <c r="Q103" t="n">
         <v>0</v>
       </c>
@@ -18558,6 +18765,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>HOLD_US_25a3245e6faa66bb52d11f87954b</t>
+        </is>
+      </c>
       <c r="AA103" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -18565,26 +18777,35 @@
       </c>
       <c r="AO103" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP103" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ103" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AR103" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS103" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS103" t="inlineStr">
+        <is>
+          <t>HOLD_US_25a3245e6faa66bb52d11f87954b</t>
+        </is>
+      </c>
       <c r="AT103" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AU103" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV103" t="inlineStr">
@@ -21528,7 +21749,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK120" t="inlineStr">
@@ -21767,7 +21988,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">
@@ -22077,6 +22298,9 @@
       <c r="O123" t="n">
         <v>0</v>
       </c>
+      <c r="P123" t="n">
+        <v>0</v>
+      </c>
       <c r="Q123" t="n">
         <v>0</v>
       </c>
@@ -22088,6 +22312,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U123" t="inlineStr">
+        <is>
+          <t>HOLD_US_25a3245e6faa66bb52d11f87954b</t>
+        </is>
+      </c>
       <c r="AA123" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -22095,26 +22324,35 @@
       </c>
       <c r="AO123" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP123" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ123" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AR123" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS123" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS123" t="inlineStr">
+        <is>
+          <t>HOLD_US_25a3245e6faa66bb52d11f87954b</t>
+        </is>
+      </c>
       <c r="AT123" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AU123" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV123" t="inlineStr">
@@ -22772,6 +23010,9 @@
       <c r="O127" t="n">
         <v>0</v>
       </c>
+      <c r="P127" t="n">
+        <v>0</v>
+      </c>
       <c r="Q127" t="n">
         <v>0</v>
       </c>
@@ -22783,6 +23024,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U127" t="inlineStr">
+        <is>
+          <t>HOLD_US_25a3245e6faa66bb52d11f87954b</t>
+        </is>
+      </c>
       <c r="AA127" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -22790,26 +23036,35 @@
       </c>
       <c r="AO127" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP127" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ127" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AR127" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS127" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS127" t="inlineStr">
+        <is>
+          <t>HOLD_US_25a3245e6faa66bb52d11f87954b</t>
+        </is>
+      </c>
       <c r="AT127" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AU127" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV127" t="inlineStr">
@@ -23467,6 +23722,9 @@
       <c r="O131" t="n">
         <v>0</v>
       </c>
+      <c r="P131" t="n">
+        <v>0</v>
+      </c>
       <c r="Q131" t="n">
         <v>0</v>
       </c>
@@ -23478,6 +23736,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U131" t="inlineStr">
+        <is>
+          <t>HOLD_US_25a3245e6faa66bb52d11f87954b</t>
+        </is>
+      </c>
       <c r="AA131" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -23485,26 +23748,35 @@
       </c>
       <c r="AO131" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP131" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ131" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AR131" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS131" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS131" t="inlineStr">
+        <is>
+          <t>HOLD_US_25a3245e6faa66bb52d11f87954b</t>
+        </is>
+      </c>
       <c r="AT131" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AU131" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV131" t="inlineStr">
@@ -24162,6 +24434,9 @@
       <c r="O135" t="n">
         <v>0</v>
       </c>
+      <c r="P135" t="n">
+        <v>0</v>
+      </c>
       <c r="Q135" t="n">
         <v>0</v>
       </c>
@@ -24173,6 +24448,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U135" t="inlineStr">
+        <is>
+          <t>HOLD_US_25a3245e6faa66bb52d11f87954b</t>
+        </is>
+      </c>
       <c r="AA135" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -24180,26 +24460,35 @@
       </c>
       <c r="AO135" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP135" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ135" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AR135" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS135" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS135" t="inlineStr">
+        <is>
+          <t>HOLD_US_25a3245e6faa66bb52d11f87954b</t>
+        </is>
+      </c>
       <c r="AT135" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AU135" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV135" t="inlineStr">
@@ -27923,7 +28212,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK156" t="inlineStr">
@@ -28162,7 +28451,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK157" t="inlineStr">
@@ -28472,6 +28761,9 @@
       <c r="O159" t="n">
         <v>0</v>
       </c>
+      <c r="P159" t="n">
+        <v>0</v>
+      </c>
       <c r="Q159" t="n">
         <v>0</v>
       </c>
@@ -28483,6 +28775,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U159" t="inlineStr">
+        <is>
+          <t>HOLD_US_25a3245e6faa66bb52d11f87954b</t>
+        </is>
+      </c>
       <c r="AA159" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -28490,26 +28787,35 @@
       </c>
       <c r="AO159" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP159" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ159" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AR159" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS159" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS159" t="inlineStr">
+        <is>
+          <t>HOLD_US_25a3245e6faa66bb52d11f87954b</t>
+        </is>
+      </c>
       <c r="AT159" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AU159" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV159" t="inlineStr">
@@ -29167,6 +29473,9 @@
       <c r="O163" t="n">
         <v>0</v>
       </c>
+      <c r="P163" t="n">
+        <v>0</v>
+      </c>
       <c r="Q163" t="n">
         <v>0</v>
       </c>
@@ -29178,6 +29487,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U163" t="inlineStr">
+        <is>
+          <t>HOLD_US_25a3245e6faa66bb52d11f87954b</t>
+        </is>
+      </c>
       <c r="AA163" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -29185,26 +29499,35 @@
       </c>
       <c r="AO163" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP163" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ163" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AR163" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS163" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS163" t="inlineStr">
+        <is>
+          <t>HOLD_US_25a3245e6faa66bb52d11f87954b</t>
+        </is>
+      </c>
       <c r="AT163" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AU163" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV163" t="inlineStr">
@@ -29862,6 +30185,9 @@
       <c r="O167" t="n">
         <v>0</v>
       </c>
+      <c r="P167" t="n">
+        <v>0</v>
+      </c>
       <c r="Q167" t="n">
         <v>0</v>
       </c>
@@ -29873,6 +30199,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U167" t="inlineStr">
+        <is>
+          <t>HOLD_US_25a3245e6faa66bb52d11f87954b</t>
+        </is>
+      </c>
       <c r="AA167" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -29880,26 +30211,35 @@
       </c>
       <c r="AO167" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP167" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ167" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AR167" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS167" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS167" t="inlineStr">
+        <is>
+          <t>HOLD_US_25a3245e6faa66bb52d11f87954b</t>
+        </is>
+      </c>
       <c r="AT167" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AU167" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV167" t="inlineStr">
@@ -30557,6 +30897,9 @@
       <c r="O171" t="n">
         <v>0</v>
       </c>
+      <c r="P171" t="n">
+        <v>0</v>
+      </c>
       <c r="Q171" t="n">
         <v>0</v>
       </c>
@@ -30568,6 +30911,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U171" t="inlineStr">
+        <is>
+          <t>HOLD_US_25a3245e6faa66bb52d11f87954b</t>
+        </is>
+      </c>
       <c r="AA171" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -30575,26 +30923,35 @@
       </c>
       <c r="AO171" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP171" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ171" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AR171" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS171" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS171" t="inlineStr">
+        <is>
+          <t>HOLD_US_25a3245e6faa66bb52d11f87954b</t>
+        </is>
+      </c>
       <c r="AT171" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AU171" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV171" t="inlineStr">
@@ -31252,6 +31609,9 @@
       <c r="O175" t="n">
         <v>0</v>
       </c>
+      <c r="P175" t="n">
+        <v>0</v>
+      </c>
       <c r="Q175" t="n">
         <v>0</v>
       </c>
@@ -31263,6 +31623,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U175" t="inlineStr">
+        <is>
+          <t>HOLD_US_25a3245e6faa66bb52d11f87954b</t>
+        </is>
+      </c>
       <c r="AA175" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -31270,26 +31635,35 @@
       </c>
       <c r="AO175" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP175" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ175" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AR175" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS175" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS175" t="inlineStr">
+        <is>
+          <t>HOLD_US_25a3245e6faa66bb52d11f87954b</t>
+        </is>
+      </c>
       <c r="AT175" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AU175" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV175" t="inlineStr">
@@ -37353,7 +37727,7 @@
       </c>
       <c r="AJ208" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK208" t="inlineStr">
@@ -37592,7 +37966,7 @@
       </c>
       <c r="AJ209" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK209" t="inlineStr">
@@ -37899,6 +38273,9 @@
       <c r="O211" t="n">
         <v>0</v>
       </c>
+      <c r="P211" t="n">
+        <v>0</v>
+      </c>
       <c r="R211" t="n">
         <v>0</v>
       </c>
@@ -37907,6 +38284,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U211" t="inlineStr">
+        <is>
+          <t>HOLD_US_25a3245e6faa66bb52d11f87954b</t>
+        </is>
+      </c>
       <c r="AA211" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -37914,26 +38296,35 @@
       </c>
       <c r="AO211" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP211" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ211" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AR211" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS211" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS211" t="inlineStr">
+        <is>
+          <t>HOLD_US_25a3245e6faa66bb52d11f87954b</t>
+        </is>
+      </c>
       <c r="AT211" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AU211" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV211" t="inlineStr">
@@ -38588,6 +38979,9 @@
       <c r="O215" t="n">
         <v>0</v>
       </c>
+      <c r="P215" t="n">
+        <v>0</v>
+      </c>
       <c r="R215" t="n">
         <v>0</v>
       </c>
@@ -38596,6 +38990,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U215" t="inlineStr">
+        <is>
+          <t>HOLD_US_25a3245e6faa66bb52d11f87954b</t>
+        </is>
+      </c>
       <c r="AA215" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -38603,26 +39002,35 @@
       </c>
       <c r="AO215" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP215" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ215" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AR215" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS215" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS215" t="inlineStr">
+        <is>
+          <t>HOLD_US_25a3245e6faa66bb52d11f87954b</t>
+        </is>
+      </c>
       <c r="AT215" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AU215" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV215" t="inlineStr">
@@ -39277,6 +39685,9 @@
       <c r="O219" t="n">
         <v>0</v>
       </c>
+      <c r="P219" t="n">
+        <v>0</v>
+      </c>
       <c r="R219" t="n">
         <v>0</v>
       </c>
@@ -39285,6 +39696,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U219" t="inlineStr">
+        <is>
+          <t>HOLD_US_25a3245e6faa66bb52d11f87954b</t>
+        </is>
+      </c>
       <c r="AA219" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -39292,26 +39708,35 @@
       </c>
       <c r="AO219" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP219" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ219" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AR219" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS219" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS219" t="inlineStr">
+        <is>
+          <t>HOLD_US_25a3245e6faa66bb52d11f87954b</t>
+        </is>
+      </c>
       <c r="AT219" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AU219" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV219" t="inlineStr">
@@ -39966,6 +40391,9 @@
       <c r="O223" t="n">
         <v>0</v>
       </c>
+      <c r="P223" t="n">
+        <v>0</v>
+      </c>
       <c r="R223" t="n">
         <v>0</v>
       </c>
@@ -39974,6 +40402,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U223" t="inlineStr">
+        <is>
+          <t>HOLD_US_25a3245e6faa66bb52d11f87954b</t>
+        </is>
+      </c>
       <c r="AA223" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -39981,26 +40414,35 @@
       </c>
       <c r="AO223" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP223" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ223" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AR223" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS223" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS223" t="inlineStr">
+        <is>
+          <t>HOLD_US_25a3245e6faa66bb52d11f87954b</t>
+        </is>
+      </c>
       <c r="AT223" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AU223" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV223" t="inlineStr">
@@ -46454,7 +46896,7 @@
       </c>
       <c r="AJ258" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK258" t="inlineStr">
@@ -46693,7 +47135,7 @@
       </c>
       <c r="AJ259" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK259" t="inlineStr">
@@ -47000,6 +47442,9 @@
       <c r="O261" t="n">
         <v>0</v>
       </c>
+      <c r="P261" t="n">
+        <v>0</v>
+      </c>
       <c r="R261" t="n">
         <v>0</v>
       </c>
@@ -47008,6 +47453,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U261" t="inlineStr">
+        <is>
+          <t>HOLD_US_25a3245e6faa66bb52d11f87954b</t>
+        </is>
+      </c>
       <c r="AA261" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -47015,26 +47465,35 @@
       </c>
       <c r="AO261" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP261" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ261" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AR261" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS261" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS261" t="inlineStr">
+        <is>
+          <t>HOLD_US_25a3245e6faa66bb52d11f87954b</t>
+        </is>
+      </c>
       <c r="AT261" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AU261" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV261" t="inlineStr">
@@ -47689,6 +48148,9 @@
       <c r="O265" t="n">
         <v>0</v>
       </c>
+      <c r="P265" t="n">
+        <v>0</v>
+      </c>
       <c r="R265" t="n">
         <v>0</v>
       </c>
@@ -47697,6 +48159,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U265" t="inlineStr">
+        <is>
+          <t>HOLD_US_25a3245e6faa66bb52d11f87954b</t>
+        </is>
+      </c>
       <c r="AA265" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -47704,26 +48171,35 @@
       </c>
       <c r="AO265" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP265" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ265" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AR265" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS265" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS265" t="inlineStr">
+        <is>
+          <t>HOLD_US_25a3245e6faa66bb52d11f87954b</t>
+        </is>
+      </c>
       <c r="AT265" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AU265" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV265" t="inlineStr">
@@ -48378,6 +48854,9 @@
       <c r="O269" t="n">
         <v>0</v>
       </c>
+      <c r="P269" t="n">
+        <v>0</v>
+      </c>
       <c r="R269" t="n">
         <v>0</v>
       </c>
@@ -48386,6 +48865,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U269" t="inlineStr">
+        <is>
+          <t>HOLD_US_25a3245e6faa66bb52d11f87954b</t>
+        </is>
+      </c>
       <c r="AA269" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -48393,26 +48877,35 @@
       </c>
       <c r="AO269" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP269" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ269" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AR269" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS269" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS269" t="inlineStr">
+        <is>
+          <t>HOLD_US_25a3245e6faa66bb52d11f87954b</t>
+        </is>
+      </c>
       <c r="AT269" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AU269" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV269" t="inlineStr">
@@ -49067,6 +49560,9 @@
       <c r="O273" t="n">
         <v>0</v>
       </c>
+      <c r="P273" t="n">
+        <v>0</v>
+      </c>
       <c r="R273" t="n">
         <v>0</v>
       </c>
@@ -49075,6 +49571,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U273" t="inlineStr">
+        <is>
+          <t>HOLD_US_25a3245e6faa66bb52d11f87954b</t>
+        </is>
+      </c>
       <c r="AA273" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -49082,26 +49583,35 @@
       </c>
       <c r="AO273" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP273" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ273" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AR273" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS273" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS273" t="inlineStr">
+        <is>
+          <t>HOLD_US_25a3245e6faa66bb52d11f87954b</t>
+        </is>
+      </c>
       <c r="AT273" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AU273" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV273" t="inlineStr">
@@ -54920,7 +55430,7 @@
       </c>
       <c r="AJ305" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK305" t="inlineStr">
@@ -55159,7 +55669,7 @@
       </c>
       <c r="AJ306" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK306" t="inlineStr">
@@ -56938,6 +57448,9 @@
       <c r="O316" t="n">
         <v>2</v>
       </c>
+      <c r="P316" t="n">
+        <v>2</v>
+      </c>
       <c r="R316" t="n">
         <v>0.0005730076265538771</v>
       </c>
@@ -56946,6 +57459,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U316" t="inlineStr">
+        <is>
+          <t>HOLD_US_25a3245e6faa66bb52d11f87954b</t>
+        </is>
+      </c>
       <c r="AA316" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -56953,26 +57471,35 @@
       </c>
       <c r="AO316" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP316" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ316" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AR316" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS316" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS316" t="inlineStr">
+        <is>
+          <t>HOLD_US_25a3245e6faa66bb52d11f87954b</t>
+        </is>
+      </c>
       <c r="AT316" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AU316" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV316" t="inlineStr">
@@ -57039,17 +57566,17 @@
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G317" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H317" t="inlineStr">
@@ -57074,7 +57601,7 @@
       </c>
       <c r="L317" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="M317" t="inlineStr">
@@ -57083,81 +57610,173 @@
         </is>
       </c>
       <c r="N317" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O317" t="n">
-        <v>0</v>
-      </c>
-      <c r="R317" t="n">
-        <v>0</v>
-      </c>
-      <c r="S317" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="P317" t="n">
+        <v>2</v>
+      </c>
+      <c r="U317" t="inlineStr">
+        <is>
+          <t>HOLD_US_25a3245e6faa66bb52d11f87954b</t>
+        </is>
+      </c>
+      <c r="V317" t="inlineStr">
+        <is>
+          <t>Novel Influenza A virus infections, Confirmed</t>
+        </is>
+      </c>
+      <c r="W317" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X317" t="inlineStr">
+        <is>
+          <t>Novel Influenza A virus infections, Confirmed</t>
+        </is>
+      </c>
+      <c r="Y317" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z317" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA317" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB317" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC317" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD317" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE317" t="inlineStr">
+        <is>
+          <t>narrower</t>
+        </is>
+      </c>
+      <c r="AF317" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG317" t="inlineStr">
+        <is>
+          <t>direct_only</t>
+        </is>
+      </c>
+      <c r="AH317" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI317" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ317" t="inlineStr">
+        <is>
+          <t>source-current</t>
+        </is>
+      </c>
+      <c r="AM317" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN317" t="b">
+        <v>1</v>
       </c>
       <c r="AO317" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP317" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ317" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AR317" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS317" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS317" t="inlineStr">
+        <is>
+          <t>HOLD_US_25a3245e6faa66bb52d11f87954b</t>
+        </is>
+      </c>
       <c r="AT317" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AU317" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV317" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW317" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX317" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY317" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ317" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA317" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB317" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC317" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -57184,17 +57803,17 @@
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G318" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H318" t="inlineStr">
@@ -57219,7 +57838,7 @@
       </c>
       <c r="L318" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="M318" t="inlineStr">
@@ -57228,20 +57847,42 @@
         </is>
       </c>
       <c r="N318" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O318" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P318" t="n">
-        <v>0</v>
-      </c>
-      <c r="R318" t="n">
-        <v>0</v>
-      </c>
-      <c r="S318" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+        <v>2</v>
+      </c>
+      <c r="U318" t="inlineStr">
+        <is>
+          <t>HOLD_US_eb406756cd20b6702c561e16999c</t>
+        </is>
+      </c>
+      <c r="V318" t="inlineStr">
+        <is>
+          <t>Novel Influenza A virus infections, Total</t>
+        </is>
+      </c>
+      <c r="W318" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X318" t="inlineStr">
+        <is>
+          <t>Novel Influenza A virus infections, Total</t>
+        </is>
+      </c>
+      <c r="Y318" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z318" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA318" t="inlineStr">
@@ -57249,72 +57890,130 @@
           <t>weekly</t>
         </is>
       </c>
+      <c r="AB318" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC318" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD318" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE318" t="inlineStr">
+        <is>
+          <t>narrower</t>
+        </is>
+      </c>
+      <c r="AF318" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG318" t="inlineStr">
+        <is>
+          <t>direct_only</t>
+        </is>
+      </c>
+      <c r="AH318" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI318" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ318" t="inlineStr">
+        <is>
+          <t>source-current</t>
+        </is>
+      </c>
+      <c r="AM318" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN318" t="b">
+        <v>0</v>
+      </c>
       <c r="AO318" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP318" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ318" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AR318" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
         </is>
       </c>
       <c r="AS318" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_AVIAN_INFLUENZA; SER_SG_HIST_AVIAN_INFLUENZA</t>
+          <t>HOLD_US_25a3245e6faa66bb52d11f87954b</t>
         </is>
       </c>
       <c r="AT318" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU318" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV318" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW318" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX318" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY318" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ318" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA318" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB318" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC318" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -57341,17 +58040,17 @@
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>US-MI</t>
         </is>
       </c>
       <c r="G319" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Michigan, United States</t>
         </is>
       </c>
       <c r="H319" t="inlineStr">
@@ -57376,7 +58075,7 @@
       </c>
       <c r="L319" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="M319" t="inlineStr">
@@ -57385,42 +58084,22 @@
         </is>
       </c>
       <c r="N319" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O319" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P319" t="n">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="S319" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
       </c>
       <c r="U319" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_AVIAN_INFLUENZA</t>
-        </is>
-      </c>
-      <c r="V319" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_AVIAN_INFLUENZA</t>
-        </is>
-      </c>
-      <c r="W319" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X319" t="inlineStr">
-        <is>
-          <t>Avian Influenza</t>
-        </is>
-      </c>
-      <c r="Y319" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z319" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+          <t>HOLD_US_25a3245e6faa66bb52d11f87954b</t>
         </is>
       </c>
       <c r="AA319" t="inlineStr">
@@ -57428,64 +58107,6 @@
           <t>weekly</t>
         </is>
       </c>
-      <c r="AB319" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC319" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD319" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE319" t="inlineStr">
-        <is>
-          <t>narrower</t>
-        </is>
-      </c>
-      <c r="AF319" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG319" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH319" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI319" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ319" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK319" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM319" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN319" t="b">
-        <v>1</v>
-      </c>
       <c r="AO319" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -57493,7 +58114,7 @@
       </c>
       <c r="AP319" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ319" t="inlineStr">
@@ -57501,9 +58122,14 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR319" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS319" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_AVIAN_INFLUENZA; SER_SG_HIST_AVIAN_INFLUENZA</t>
+          <t>HOLD_US_25a3245e6faa66bb52d11f87954b</t>
         </is>
       </c>
       <c r="AT319" t="n">
@@ -57511,47 +58137,47 @@
       </c>
       <c r="AU319" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV319" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW319" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX319" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
         </is>
       </c>
       <c r="AY319" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ319" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="BA319" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="BB319" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
         </is>
       </c>
       <c r="BC319" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -57578,17 +58204,17 @@
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US-MI</t>
         </is>
       </c>
       <c r="G320" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Michigan, United States</t>
         </is>
       </c>
       <c r="H320" t="inlineStr">
@@ -57613,7 +58239,7 @@
       </c>
       <c r="L320" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="M320" t="inlineStr">
@@ -57622,56 +58248,148 @@
         </is>
       </c>
       <c r="N320" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O320" t="n">
-        <v>0</v>
-      </c>
-      <c r="R320" t="n">
-        <v>0</v>
-      </c>
-      <c r="S320" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="P320" t="n">
+        <v>2</v>
+      </c>
+      <c r="U320" t="inlineStr">
+        <is>
+          <t>HOLD_US_25a3245e6faa66bb52d11f87954b</t>
+        </is>
+      </c>
+      <c r="V320" t="inlineStr">
+        <is>
+          <t>Novel Influenza A virus infections, Confirmed</t>
+        </is>
+      </c>
+      <c r="W320" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X320" t="inlineStr">
+        <is>
+          <t>Novel Influenza A virus infections, Confirmed</t>
+        </is>
+      </c>
+      <c r="Y320" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z320" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA320" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB320" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC320" t="inlineStr">
+        <is>
+          <t>country:US-MI:national</t>
+        </is>
+      </c>
+      <c r="AD320" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE320" t="inlineStr">
+        <is>
+          <t>narrower</t>
+        </is>
+      </c>
+      <c r="AF320" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG320" t="inlineStr">
+        <is>
+          <t>direct_only</t>
+        </is>
+      </c>
+      <c r="AH320" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI320" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ320" t="inlineStr">
+        <is>
+          <t>source-current</t>
+        </is>
+      </c>
+      <c r="AM320" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN320" t="b">
+        <v>1</v>
       </c>
       <c r="AO320" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP320" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ320" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR320" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS320" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS320" t="inlineStr">
+        <is>
+          <t>HOLD_US_25a3245e6faa66bb52d11f87954b</t>
+        </is>
+      </c>
       <c r="AT320" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU320" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV320" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW320" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX320" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
         </is>
       </c>
       <c r="AY320" t="inlineStr">
@@ -57681,17 +58399,17 @@
       </c>
       <c r="AZ320" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="BA320" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="BB320" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
         </is>
       </c>
       <c r="BC320" t="inlineStr">
@@ -57723,17 +58441,17 @@
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>US-MI</t>
         </is>
       </c>
       <c r="G321" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Michigan, United States</t>
         </is>
       </c>
       <c r="H321" t="inlineStr">
@@ -57758,7 +58476,7 @@
       </c>
       <c r="L321" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="M321" t="inlineStr">
@@ -57767,20 +58485,42 @@
         </is>
       </c>
       <c r="N321" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O321" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P321" t="n">
-        <v>0</v>
-      </c>
-      <c r="R321" t="n">
-        <v>0</v>
-      </c>
-      <c r="S321" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+        <v>2</v>
+      </c>
+      <c r="U321" t="inlineStr">
+        <is>
+          <t>HOLD_US_eb406756cd20b6702c561e16999c</t>
+        </is>
+      </c>
+      <c r="V321" t="inlineStr">
+        <is>
+          <t>Novel Influenza A virus infections, Total</t>
+        </is>
+      </c>
+      <c r="W321" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X321" t="inlineStr">
+        <is>
+          <t>Novel Influenza A virus infections, Total</t>
+        </is>
+      </c>
+      <c r="Y321" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z321" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA321" t="inlineStr">
@@ -57788,6 +58528,59 @@
           <t>weekly</t>
         </is>
       </c>
+      <c r="AB321" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC321" t="inlineStr">
+        <is>
+          <t>country:US-MI:national</t>
+        </is>
+      </c>
+      <c r="AD321" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE321" t="inlineStr">
+        <is>
+          <t>narrower</t>
+        </is>
+      </c>
+      <c r="AF321" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG321" t="inlineStr">
+        <is>
+          <t>direct_only</t>
+        </is>
+      </c>
+      <c r="AH321" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI321" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ321" t="inlineStr">
+        <is>
+          <t>source-current</t>
+        </is>
+      </c>
+      <c r="AM321" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN321" t="b">
+        <v>0</v>
+      </c>
       <c r="AO321" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -57795,7 +58588,7 @@
       </c>
       <c r="AP321" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ321" t="inlineStr">
@@ -57803,9 +58596,14 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR321" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS321" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_AVIAN_INFLUENZA; SER_SG_HIST_AVIAN_INFLUENZA</t>
+          <t>HOLD_US_25a3245e6faa66bb52d11f87954b</t>
         </is>
       </c>
       <c r="AT321" t="n">
@@ -57813,47 +58611,47 @@
       </c>
       <c r="AU321" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV321" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW321" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX321" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
         </is>
       </c>
       <c r="AY321" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ321" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="BA321" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="BB321" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
         </is>
       </c>
       <c r="BC321" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -57880,17 +58678,17 @@
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G322" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H322" t="inlineStr">
@@ -57915,7 +58713,7 @@
       </c>
       <c r="L322" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M322" t="inlineStr">
@@ -57929,168 +58727,76 @@
       <c r="O322" t="n">
         <v>0</v>
       </c>
-      <c r="P322" t="n">
-        <v>0</v>
-      </c>
-      <c r="U322" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_AVIAN_INFLUENZA</t>
-        </is>
-      </c>
-      <c r="V322" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_AVIAN_INFLUENZA</t>
-        </is>
-      </c>
-      <c r="W322" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X322" t="inlineStr">
-        <is>
-          <t>Avian Influenza</t>
-        </is>
-      </c>
-      <c r="Y322" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z322" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA322" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB322" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC322" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD322" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE322" t="inlineStr">
-        <is>
-          <t>narrower</t>
-        </is>
-      </c>
-      <c r="AF322" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG322" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH322" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI322" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ322" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK322" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM322" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN322" t="b">
-        <v>1</v>
+      <c r="R322" t="n">
+        <v>0</v>
+      </c>
+      <c r="S322" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO322" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP322" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ322" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS322" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_AVIAN_INFLUENZA; SER_SG_HIST_AVIAN_INFLUENZA</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR322" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS322" t="inlineStr"/>
       <c r="AT322" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU322" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV322" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW322" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX322" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY322" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ322" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA322" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB322" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC322" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -58122,12 +58828,12 @@
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G323" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H323" t="inlineStr">
@@ -58152,12 +58858,12 @@
       </c>
       <c r="L323" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M323" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N323" t="n">
@@ -58166,6 +58872,9 @@
       <c r="O323" t="n">
         <v>0</v>
       </c>
+      <c r="P323" t="n">
+        <v>0</v>
+      </c>
       <c r="R323" t="n">
         <v>0</v>
       </c>
@@ -58176,71 +58885,75 @@
       </c>
       <c r="AA323" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO323" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP323" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR323" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS323" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ323" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS323" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_AVIAN_INFLUENZA; SER_SG_HIST_AVIAN_INFLUENZA</t>
+        </is>
+      </c>
       <c r="AT323" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU323" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV323" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW323" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX323" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY323" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ323" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA323" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB323" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC323" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -58267,17 +58980,17 @@
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>AU-ACT</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t>Australian Capital Territory, Australia</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H324" t="inlineStr">
@@ -58302,12 +59015,12 @@
       </c>
       <c r="L324" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M324" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N324" t="n">
@@ -58316,81 +59029,168 @@
       <c r="O324" t="n">
         <v>0</v>
       </c>
-      <c r="R324" t="n">
-        <v>0</v>
-      </c>
-      <c r="S324" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
+      <c r="P324" t="n">
+        <v>0</v>
+      </c>
+      <c r="U324" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_AVIAN_INFLUENZA</t>
+        </is>
+      </c>
+      <c r="V324" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_AVIAN_INFLUENZA</t>
+        </is>
+      </c>
+      <c r="W324" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X324" t="inlineStr">
+        <is>
+          <t>Avian Influenza</t>
+        </is>
+      </c>
+      <c r="Y324" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z324" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA324" t="inlineStr">
         <is>
-          <t>monthly</t>
-        </is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB324" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC324" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD324" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE324" t="inlineStr">
+        <is>
+          <t>narrower</t>
+        </is>
+      </c>
+      <c r="AF324" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG324" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH324" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI324" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ324" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK324" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM324" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN324" t="b">
+        <v>1</v>
       </c>
       <c r="AO324" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP324" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR324" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS324" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ324" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS324" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_AVIAN_INFLUENZA; SER_SG_HIST_AVIAN_INFLUENZA</t>
+        </is>
+      </c>
       <c r="AT324" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU324" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV324" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW324" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Australian Capital Territory</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX324" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY324" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ324" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA324" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Australian Capital Territory</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB324" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC324" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -58422,12 +59222,12 @@
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>AU-NSW</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G325" t="inlineStr">
         <is>
-          <t>New South Wales, Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H325" t="inlineStr">
@@ -58452,12 +59252,12 @@
       </c>
       <c r="L325" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M325" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N325" t="n">
@@ -58471,12 +59271,7 @@
       </c>
       <c r="S325" t="inlineStr">
         <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
-      <c r="AA325" t="inlineStr">
-        <is>
-          <t>monthly</t>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AO325" t="inlineStr">
@@ -58505,42 +59300,42 @@
       </c>
       <c r="AV325" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW325" t="inlineStr">
         <is>
-          <t>Australia NINDSS — New South Wales</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX325" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY325" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ325" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA325" t="inlineStr">
         <is>
-          <t>Australia NINDSS — New South Wales</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB325" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC325" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -58572,12 +59367,12 @@
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>AU-NT</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G326" t="inlineStr">
         <is>
-          <t>Northern Territory, Australia</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H326" t="inlineStr">
@@ -58602,12 +59397,12 @@
       </c>
       <c r="L326" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M326" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N326" t="n">
@@ -58616,81 +59411,88 @@
       <c r="O326" t="n">
         <v>0</v>
       </c>
+      <c r="P326" t="n">
+        <v>0</v>
+      </c>
       <c r="R326" t="n">
         <v>0</v>
       </c>
       <c r="S326" t="inlineStr">
         <is>
-          <t>abs_computed</t>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA326" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO326" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP326" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR326" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS326" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ326" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS326" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_AVIAN_INFLUENZA; SER_SG_HIST_AVIAN_INFLUENZA</t>
+        </is>
+      </c>
       <c r="AT326" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU326" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV326" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW326" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Northern Territory</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX326" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY326" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ326" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA326" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Northern Territory</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB326" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC326" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -58717,17 +59519,17 @@
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>AU-QLD</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G327" t="inlineStr">
         <is>
-          <t>Queensland, Australia</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H327" t="inlineStr">
@@ -58752,12 +59554,12 @@
       </c>
       <c r="L327" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M327" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N327" t="n">
@@ -58766,81 +59568,168 @@
       <c r="O327" t="n">
         <v>0</v>
       </c>
-      <c r="R327" t="n">
-        <v>0</v>
-      </c>
-      <c r="S327" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
+      <c r="P327" t="n">
+        <v>0</v>
+      </c>
+      <c r="U327" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_AVIAN_INFLUENZA</t>
+        </is>
+      </c>
+      <c r="V327" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_AVIAN_INFLUENZA</t>
+        </is>
+      </c>
+      <c r="W327" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X327" t="inlineStr">
+        <is>
+          <t>Avian Influenza</t>
+        </is>
+      </c>
+      <c r="Y327" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z327" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA327" t="inlineStr">
         <is>
-          <t>monthly</t>
-        </is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB327" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC327" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD327" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE327" t="inlineStr">
+        <is>
+          <t>narrower</t>
+        </is>
+      </c>
+      <c r="AF327" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG327" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH327" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI327" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ327" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK327" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM327" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN327" t="b">
+        <v>1</v>
       </c>
       <c r="AO327" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP327" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR327" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS327" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ327" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS327" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_AVIAN_INFLUENZA; SER_SG_HIST_AVIAN_INFLUENZA</t>
+        </is>
+      </c>
       <c r="AT327" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU327" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV327" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW327" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Queensland</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX327" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY327" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ327" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA327" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Queensland</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB327" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC327" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -58872,12 +59761,12 @@
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>AU-SA</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G328" t="inlineStr">
         <is>
-          <t>South Australia, Australia</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H328" t="inlineStr">
@@ -58921,7 +59810,7 @@
       </c>
       <c r="S328" t="inlineStr">
         <is>
-          <t>abs_computed</t>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA328" t="inlineStr">
@@ -58960,12 +59849,12 @@
       </c>
       <c r="AW328" t="inlineStr">
         <is>
-          <t>Australia NINDSS — South Australia</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX328" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY328" t="inlineStr">
@@ -58980,12 +59869,12 @@
       </c>
       <c r="BA328" t="inlineStr">
         <is>
-          <t>Australia NINDSS — South Australia</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB328" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC328" t="inlineStr">
@@ -59022,12 +59911,12 @@
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>AU-TAS</t>
+          <t>AU-ACT</t>
         </is>
       </c>
       <c r="G329" t="inlineStr">
         <is>
-          <t>Tasmania, Australia</t>
+          <t>Australian Capital Territory, Australia</t>
         </is>
       </c>
       <c r="H329" t="inlineStr">
@@ -59110,7 +59999,7 @@
       </c>
       <c r="AW329" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Tasmania</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="AX329" t="inlineStr">
@@ -59130,7 +60019,7 @@
       </c>
       <c r="BA329" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Tasmania</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="BB329" t="inlineStr">
@@ -59172,12 +60061,12 @@
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>AU-VIC</t>
+          <t>AU-NSW</t>
         </is>
       </c>
       <c r="G330" t="inlineStr">
         <is>
-          <t>Victoria, Australia</t>
+          <t>New South Wales, Australia</t>
         </is>
       </c>
       <c r="H330" t="inlineStr">
@@ -59260,7 +60149,7 @@
       </c>
       <c r="AW330" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Victoria</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="AX330" t="inlineStr">
@@ -59280,7 +60169,7 @@
       </c>
       <c r="BA330" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Victoria</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="BB330" t="inlineStr">
@@ -59322,12 +60211,12 @@
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>AU-WA</t>
+          <t>AU-NT</t>
         </is>
       </c>
       <c r="G331" t="inlineStr">
         <is>
-          <t>Western Australia, Australia</t>
+          <t>Northern Territory, Australia</t>
         </is>
       </c>
       <c r="H331" t="inlineStr">
@@ -59410,7 +60299,7 @@
       </c>
       <c r="AW331" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Western Australia</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="AX331" t="inlineStr">
@@ -59430,7 +60319,7 @@
       </c>
       <c r="BA331" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Western Australia</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="BB331" t="inlineStr">
@@ -59472,12 +60361,12 @@
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>AU-QLD</t>
         </is>
       </c>
       <c r="G332" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Queensland, Australia</t>
         </is>
       </c>
       <c r="H332" t="inlineStr">
@@ -59521,12 +60410,7 @@
       </c>
       <c r="S332" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U332" t="inlineStr">
-        <is>
-          <t>SER_KR_ANIMAL_INFLUENZA_HUMAN_INFECTION</t>
+          <t>abs_computed</t>
         </is>
       </c>
       <c r="AA332" t="inlineStr">
@@ -59536,75 +60420,66 @@
       </c>
       <c r="AO332" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP332" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ332" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR332" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS332" t="inlineStr">
-        <is>
-          <t>SER_KR_ANIMAL_INFLUENZA_HUMAN_INFECTION</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS332" t="inlineStr"/>
       <c r="AT332" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU332" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV332" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW332" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="AX332" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY332" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ332" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA332" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="BB332" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC332" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -59631,17 +60506,17 @@
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>AU-SA</t>
         </is>
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>South Australia, Australia</t>
         </is>
       </c>
       <c r="H333" t="inlineStr">
@@ -59680,34 +60555,12 @@
       <c r="O333" t="n">
         <v>0</v>
       </c>
-      <c r="U333" t="inlineStr">
-        <is>
-          <t>SER_KR_ANIMAL_INFLUENZA_HUMAN_INFECTION</t>
-        </is>
-      </c>
-      <c r="V333" t="inlineStr">
-        <is>
-          <t>SER_KR_ANIMAL_INFLUENZA_HUMAN_INFECTION</t>
-        </is>
-      </c>
-      <c r="W333" t="inlineStr">
-        <is>
-          <t>SRC_KR_KDCA</t>
-        </is>
-      </c>
-      <c r="X333" t="inlineStr">
-        <is>
-          <t>동물인플루엔자 인체감염증</t>
-        </is>
-      </c>
-      <c r="Y333" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z333" t="inlineStr">
-        <is>
-          <t>notification</t>
+      <c r="R333" t="n">
+        <v>0</v>
+      </c>
+      <c r="S333" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
         </is>
       </c>
       <c r="AA333" t="inlineStr">
@@ -59715,135 +60568,68 @@
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB333" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC333" t="inlineStr">
-        <is>
-          <t>country:KR:national</t>
-        </is>
-      </c>
-      <c r="AD333" t="inlineStr">
+      <c r="AO333" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP333" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR333" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS333" t="inlineStr"/>
+      <c r="AT333" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU333" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV333" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE333" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF333" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG333" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH333" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI333" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ333" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
-        </is>
-      </c>
-      <c r="AK333" t="inlineStr">
-        <is>
-          <t>Korea KDCA animal influenza infection in humans, retained separately from the generic novel influenza category.</t>
-        </is>
-      </c>
-      <c r="AM333" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN333" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO333" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP333" t="inlineStr">
-        <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ333" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AR333" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS333" t="inlineStr">
-        <is>
-          <t>SER_KR_ANIMAL_INFLUENZA_HUMAN_INFECTION</t>
-        </is>
-      </c>
-      <c r="AT333" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU333" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
-        </is>
-      </c>
-      <c r="AV333" t="inlineStr">
-        <is>
-          <t>kdca_open_api</t>
-        </is>
-      </c>
       <c r="AW333" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="AX333" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY333" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ333" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA333" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="BB333" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC333" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -59870,17 +60656,17 @@
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>AU-TAS</t>
         </is>
       </c>
       <c r="G334" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Tasmania, Australia</t>
         </is>
       </c>
       <c r="H334" t="inlineStr">
@@ -59919,34 +60705,12 @@
       <c r="O334" t="n">
         <v>0</v>
       </c>
-      <c r="U334" t="inlineStr">
-        <is>
-          <t>SER_KR_NOVEL_INFLUENZA</t>
-        </is>
-      </c>
-      <c r="V334" t="inlineStr">
-        <is>
-          <t>SER_KR_NOVEL_INFLUENZA</t>
-        </is>
-      </c>
-      <c r="W334" t="inlineStr">
-        <is>
-          <t>SRC_KR_KDCA</t>
-        </is>
-      </c>
-      <c r="X334" t="inlineStr">
-        <is>
-          <t>신종인플루엔자</t>
-        </is>
-      </c>
-      <c r="Y334" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z334" t="inlineStr">
-        <is>
-          <t>notification</t>
+      <c r="R334" t="n">
+        <v>0</v>
+      </c>
+      <c r="S334" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
         </is>
       </c>
       <c r="AA334" t="inlineStr">
@@ -59954,135 +60718,68 @@
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB334" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC334" t="inlineStr">
-        <is>
-          <t>country:KR:national</t>
-        </is>
-      </c>
-      <c r="AD334" t="inlineStr">
+      <c r="AO334" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP334" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR334" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS334" t="inlineStr"/>
+      <c r="AT334" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU334" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV334" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE334" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF334" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG334" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH334" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI334" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ334" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
-        </is>
-      </c>
-      <c r="AK334" t="inlineStr">
-        <is>
-          <t>Korea KDCA novel influenza category.</t>
-        </is>
-      </c>
-      <c r="AM334" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN334" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO334" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP334" t="inlineStr">
-        <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ334" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AR334" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS334" t="inlineStr">
-        <is>
-          <t>SER_KR_ANIMAL_INFLUENZA_HUMAN_INFECTION</t>
-        </is>
-      </c>
-      <c r="AT334" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU334" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
-        </is>
-      </c>
-      <c r="AV334" t="inlineStr">
-        <is>
-          <t>kdca_open_api</t>
-        </is>
-      </c>
       <c r="AW334" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="AX334" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY334" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ334" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA334" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="BB334" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC334" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -60114,12 +60811,12 @@
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>AU-VIC</t>
         </is>
       </c>
       <c r="G335" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Victoria, Australia</t>
         </is>
       </c>
       <c r="H335" t="inlineStr">
@@ -60144,7 +60841,7 @@
       </c>
       <c r="L335" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="M335" t="inlineStr">
@@ -60163,7 +60860,12 @@
       </c>
       <c r="S335" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>abs_computed</t>
+        </is>
+      </c>
+      <c r="AA335" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO335" t="inlineStr">
@@ -60192,42 +60894,42 @@
       </c>
       <c r="AV335" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW335" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="AX335" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY335" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ335" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA335" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="BB335" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC335" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -60259,12 +60961,12 @@
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>AU-WA</t>
         </is>
       </c>
       <c r="G336" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Western Australia, Australia</t>
         </is>
       </c>
       <c r="H336" t="inlineStr">
@@ -60289,7 +60991,7 @@
       </c>
       <c r="L336" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="M336" t="inlineStr">
@@ -60303,88 +61005,81 @@
       <c r="O336" t="n">
         <v>0</v>
       </c>
-      <c r="P336" t="n">
-        <v>0</v>
-      </c>
       <c r="R336" t="n">
         <v>0</v>
       </c>
       <c r="S336" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>abs_computed</t>
         </is>
       </c>
       <c r="AA336" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO336" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP336" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ336" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS336" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_AVIAN_INFLUENZA; SER_SG_HIST_AVIAN_INFLUENZA</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR336" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS336" t="inlineStr"/>
       <c r="AT336" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU336" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV336" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW336" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="AX336" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY336" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ336" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA336" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="BB336" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC336" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -60411,17 +61106,17 @@
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G337" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H337" t="inlineStr">
@@ -60446,7 +61141,7 @@
       </c>
       <c r="L337" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="M337" t="inlineStr">
@@ -60460,101 +61155,23 @@
       <c r="O337" t="n">
         <v>0</v>
       </c>
-      <c r="P337" t="n">
-        <v>0</v>
+      <c r="R337" t="n">
+        <v>0</v>
+      </c>
+      <c r="S337" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="U337" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_AVIAN_INFLUENZA</t>
-        </is>
-      </c>
-      <c r="V337" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_AVIAN_INFLUENZA</t>
-        </is>
-      </c>
-      <c r="W337" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X337" t="inlineStr">
-        <is>
-          <t>Avian Influenza</t>
-        </is>
-      </c>
-      <c r="Y337" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z337" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+          <t>SER_KR_ANIMAL_INFLUENZA_HUMAN_INFECTION</t>
         </is>
       </c>
       <c r="AA337" t="inlineStr">
         <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB337" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC337" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD337" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE337" t="inlineStr">
-        <is>
-          <t>narrower</t>
-        </is>
-      </c>
-      <c r="AF337" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG337" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH337" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI337" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ337" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK337" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM337" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN337" t="b">
-        <v>1</v>
+          <t>monthly</t>
+        </is>
       </c>
       <c r="AO337" t="inlineStr">
         <is>
@@ -60563,7 +61180,7 @@
       </c>
       <c r="AP337" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ337" t="inlineStr">
@@ -60571,9 +61188,14 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR337" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS337" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_AVIAN_INFLUENZA; SER_SG_HIST_AVIAN_INFLUENZA</t>
+          <t>SER_KR_ANIMAL_INFLUENZA_HUMAN_INFECTION</t>
         </is>
       </c>
       <c r="AT337" t="n">
@@ -60581,47 +61203,47 @@
       </c>
       <c r="AU337" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV337" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW337" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX337" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY337" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ337" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA337" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB337" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC337" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -60648,17 +61270,17 @@
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G338" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H338" t="inlineStr">
@@ -60683,7 +61305,7 @@
       </c>
       <c r="L338" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="M338" t="inlineStr">
@@ -60697,76 +61319,170 @@
       <c r="O338" t="n">
         <v>0</v>
       </c>
-      <c r="R338" t="n">
-        <v>0</v>
-      </c>
-      <c r="S338" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="U338" t="inlineStr">
+        <is>
+          <t>SER_KR_ANIMAL_INFLUENZA_HUMAN_INFECTION</t>
+        </is>
+      </c>
+      <c r="V338" t="inlineStr">
+        <is>
+          <t>SER_KR_ANIMAL_INFLUENZA_HUMAN_INFECTION</t>
+        </is>
+      </c>
+      <c r="W338" t="inlineStr">
+        <is>
+          <t>SRC_KR_KDCA</t>
+        </is>
+      </c>
+      <c r="X338" t="inlineStr">
+        <is>
+          <t>동물인플루엔자 인체감염증</t>
+        </is>
+      </c>
+      <c r="Y338" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z338" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA338" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB338" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC338" t="inlineStr">
+        <is>
+          <t>country:KR:national</t>
+        </is>
+      </c>
+      <c r="AD338" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE338" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF338" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG338" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH338" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI338" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ338" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
+        </is>
+      </c>
+      <c r="AK338" t="inlineStr">
+        <is>
+          <t>Korea KDCA animal influenza infection in humans, retained separately from the generic novel influenza category.</t>
+        </is>
+      </c>
+      <c r="AM338" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN338" t="b">
+        <v>1</v>
       </c>
       <c r="AO338" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP338" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ338" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR338" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS338" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS338" t="inlineStr">
+        <is>
+          <t>SER_KR_ANIMAL_INFLUENZA_HUMAN_INFECTION</t>
+        </is>
+      </c>
       <c r="AT338" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU338" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV338" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW338" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX338" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY338" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ338" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA338" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB338" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC338" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -60793,17 +61509,17 @@
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G339" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H339" t="inlineStr">
@@ -60828,7 +61544,7 @@
       </c>
       <c r="L339" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="M339" t="inlineStr">
@@ -60842,21 +61558,98 @@
       <c r="O339" t="n">
         <v>0</v>
       </c>
-      <c r="P339" t="n">
-        <v>0</v>
-      </c>
-      <c r="R339" t="n">
-        <v>0</v>
-      </c>
-      <c r="S339" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+      <c r="U339" t="inlineStr">
+        <is>
+          <t>SER_KR_NOVEL_INFLUENZA</t>
+        </is>
+      </c>
+      <c r="V339" t="inlineStr">
+        <is>
+          <t>SER_KR_NOVEL_INFLUENZA</t>
+        </is>
+      </c>
+      <c r="W339" t="inlineStr">
+        <is>
+          <t>SRC_KR_KDCA</t>
+        </is>
+      </c>
+      <c r="X339" t="inlineStr">
+        <is>
+          <t>신종인플루엔자</t>
+        </is>
+      </c>
+      <c r="Y339" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z339" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA339" t="inlineStr">
         <is>
-          <t>weekly</t>
-        </is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB339" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC339" t="inlineStr">
+        <is>
+          <t>country:KR:national</t>
+        </is>
+      </c>
+      <c r="AD339" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE339" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF339" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG339" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH339" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI339" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ339" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
+        </is>
+      </c>
+      <c r="AK339" t="inlineStr">
+        <is>
+          <t>Korea KDCA novel influenza category.</t>
+        </is>
+      </c>
+      <c r="AM339" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN339" t="b">
+        <v>0</v>
       </c>
       <c r="AO339" t="inlineStr">
         <is>
@@ -60865,7 +61658,7 @@
       </c>
       <c r="AP339" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ339" t="inlineStr">
@@ -60873,9 +61666,14 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR339" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS339" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_AVIAN_INFLUENZA; SER_SG_HIST_AVIAN_INFLUENZA</t>
+          <t>SER_KR_ANIMAL_INFLUENZA_HUMAN_INFECTION</t>
         </is>
       </c>
       <c r="AT339" t="n">
@@ -60883,47 +61681,47 @@
       </c>
       <c r="AU339" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV339" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW339" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX339" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY339" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ339" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA339" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB339" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC339" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -60950,17 +61748,17 @@
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G340" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H340" t="inlineStr">
@@ -60985,7 +61783,7 @@
       </c>
       <c r="L340" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="M340" t="inlineStr">
@@ -60999,168 +61797,76 @@
       <c r="O340" t="n">
         <v>0</v>
       </c>
-      <c r="P340" t="n">
-        <v>0</v>
-      </c>
-      <c r="U340" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_AVIAN_INFLUENZA</t>
-        </is>
-      </c>
-      <c r="V340" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_AVIAN_INFLUENZA</t>
-        </is>
-      </c>
-      <c r="W340" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X340" t="inlineStr">
-        <is>
-          <t>Avian Influenza</t>
-        </is>
-      </c>
-      <c r="Y340" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z340" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA340" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB340" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC340" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD340" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE340" t="inlineStr">
-        <is>
-          <t>narrower</t>
-        </is>
-      </c>
-      <c r="AF340" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG340" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH340" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI340" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ340" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK340" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM340" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN340" t="b">
-        <v>1</v>
+      <c r="R340" t="n">
+        <v>0</v>
+      </c>
+      <c r="S340" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO340" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP340" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ340" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS340" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_AVIAN_INFLUENZA; SER_SG_HIST_AVIAN_INFLUENZA</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR340" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS340" t="inlineStr"/>
       <c r="AT340" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU340" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV340" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW340" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX340" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY340" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ340" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA340" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB340" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC340" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -61192,12 +61898,12 @@
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G341" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H341" t="inlineStr">
@@ -61222,7 +61928,7 @@
       </c>
       <c r="L341" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="M341" t="inlineStr">
@@ -61236,6 +61942,9 @@
       <c r="O341" t="n">
         <v>0</v>
       </c>
+      <c r="P341" t="n">
+        <v>0</v>
+      </c>
       <c r="R341" t="n">
         <v>0</v>
       </c>
@@ -61244,68 +61953,77 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA341" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO341" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP341" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR341" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS341" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ341" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS341" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_AVIAN_INFLUENZA; SER_SG_HIST_AVIAN_INFLUENZA</t>
+        </is>
+      </c>
       <c r="AT341" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU341" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV341" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW341" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX341" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY341" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ341" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA341" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB341" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC341" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -61332,7 +62050,7 @@
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F342" t="inlineStr">
@@ -61367,7 +62085,7 @@
       </c>
       <c r="L342" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="M342" t="inlineStr">
@@ -61384,18 +62102,98 @@
       <c r="P342" t="n">
         <v>0</v>
       </c>
-      <c r="R342" t="n">
-        <v>0</v>
-      </c>
-      <c r="S342" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+      <c r="U342" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_AVIAN_INFLUENZA</t>
+        </is>
+      </c>
+      <c r="V342" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_AVIAN_INFLUENZA</t>
+        </is>
+      </c>
+      <c r="W342" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X342" t="inlineStr">
+        <is>
+          <t>Avian Influenza</t>
+        </is>
+      </c>
+      <c r="Y342" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z342" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA342" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB342" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC342" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD342" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE342" t="inlineStr">
+        <is>
+          <t>narrower</t>
+        </is>
+      </c>
+      <c r="AF342" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG342" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH342" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI342" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ342" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK342" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM342" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN342" t="b">
+        <v>1</v>
       </c>
       <c r="AO342" t="inlineStr">
         <is>
@@ -61489,17 +62287,17 @@
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G343" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H343" t="inlineStr">
@@ -61524,7 +62322,7 @@
       </c>
       <c r="L343" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="M343" t="inlineStr">
@@ -61538,168 +62336,76 @@
       <c r="O343" t="n">
         <v>0</v>
       </c>
-      <c r="P343" t="n">
-        <v>0</v>
-      </c>
-      <c r="U343" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_AVIAN_INFLUENZA</t>
-        </is>
-      </c>
-      <c r="V343" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_AVIAN_INFLUENZA</t>
-        </is>
-      </c>
-      <c r="W343" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X343" t="inlineStr">
-        <is>
-          <t>Avian Influenza</t>
-        </is>
-      </c>
-      <c r="Y343" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z343" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA343" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB343" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC343" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD343" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE343" t="inlineStr">
-        <is>
-          <t>narrower</t>
-        </is>
-      </c>
-      <c r="AF343" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG343" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH343" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI343" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ343" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK343" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM343" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN343" t="b">
-        <v>1</v>
+      <c r="R343" t="n">
+        <v>0</v>
+      </c>
+      <c r="S343" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO343" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP343" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ343" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS343" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_AVIAN_INFLUENZA; SER_SG_HIST_AVIAN_INFLUENZA</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR343" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS343" t="inlineStr"/>
       <c r="AT343" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU343" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV343" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW343" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX343" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY343" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ343" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA343" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB343" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC343" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -61731,12 +62437,12 @@
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G344" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H344" t="inlineStr">
@@ -61761,7 +62467,7 @@
       </c>
       <c r="L344" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="M344" t="inlineStr">
@@ -61775,6 +62481,9 @@
       <c r="O344" t="n">
         <v>0</v>
       </c>
+      <c r="P344" t="n">
+        <v>0</v>
+      </c>
       <c r="R344" t="n">
         <v>0</v>
       </c>
@@ -61783,68 +62492,77 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA344" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO344" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP344" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR344" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS344" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ344" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS344" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_AVIAN_INFLUENZA; SER_SG_HIST_AVIAN_INFLUENZA</t>
+        </is>
+      </c>
       <c r="AT344" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU344" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV344" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW344" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX344" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY344" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ344" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA344" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB344" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC344" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -61871,7 +62589,7 @@
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F345" t="inlineStr">
@@ -61906,7 +62624,7 @@
       </c>
       <c r="L345" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="M345" t="inlineStr">
@@ -61923,18 +62641,98 @@
       <c r="P345" t="n">
         <v>0</v>
       </c>
-      <c r="R345" t="n">
-        <v>0</v>
-      </c>
-      <c r="S345" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+      <c r="U345" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_AVIAN_INFLUENZA</t>
+        </is>
+      </c>
+      <c r="V345" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_AVIAN_INFLUENZA</t>
+        </is>
+      </c>
+      <c r="W345" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X345" t="inlineStr">
+        <is>
+          <t>Avian Influenza</t>
+        </is>
+      </c>
+      <c r="Y345" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z345" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA345" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB345" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC345" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD345" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE345" t="inlineStr">
+        <is>
+          <t>narrower</t>
+        </is>
+      </c>
+      <c r="AF345" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG345" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH345" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI345" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ345" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK345" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM345" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN345" t="b">
+        <v>1</v>
       </c>
       <c r="AO345" t="inlineStr">
         <is>
@@ -62028,17 +62826,17 @@
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G346" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H346" t="inlineStr">
@@ -62063,7 +62861,7 @@
       </c>
       <c r="L346" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="M346" t="inlineStr">
@@ -62077,168 +62875,76 @@
       <c r="O346" t="n">
         <v>0</v>
       </c>
-      <c r="P346" t="n">
-        <v>0</v>
-      </c>
-      <c r="U346" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_AVIAN_INFLUENZA</t>
-        </is>
-      </c>
-      <c r="V346" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_AVIAN_INFLUENZA</t>
-        </is>
-      </c>
-      <c r="W346" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X346" t="inlineStr">
-        <is>
-          <t>Avian Influenza</t>
-        </is>
-      </c>
-      <c r="Y346" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z346" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA346" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB346" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC346" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD346" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE346" t="inlineStr">
-        <is>
-          <t>narrower</t>
-        </is>
-      </c>
-      <c r="AF346" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG346" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH346" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI346" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ346" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK346" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM346" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN346" t="b">
-        <v>1</v>
+      <c r="R346" t="n">
+        <v>0</v>
+      </c>
+      <c r="S346" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO346" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP346" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ346" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS346" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_AVIAN_INFLUENZA; SER_SG_HIST_AVIAN_INFLUENZA</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR346" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS346" t="inlineStr"/>
       <c r="AT346" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU346" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV346" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW346" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX346" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY346" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ346" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA346" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB346" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC346" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -62270,12 +62976,12 @@
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G347" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H347" t="inlineStr">
@@ -62300,12 +63006,12 @@
       </c>
       <c r="L347" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="M347" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="N347" t="n">
@@ -62314,6 +63020,9 @@
       <c r="O347" t="n">
         <v>0</v>
       </c>
+      <c r="P347" t="n">
+        <v>0</v>
+      </c>
       <c r="R347" t="n">
         <v>0</v>
       </c>
@@ -62322,14 +63031,9 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U347" t="inlineStr">
-        <is>
-          <t>SER_KR_ANIMAL_INFLUENZA_HUMAN_INFECTION</t>
-        </is>
-      </c>
       <c r="AA347" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO347" t="inlineStr">
@@ -62339,7 +63043,7 @@
       </c>
       <c r="AP347" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>temporal_handoff</t>
         </is>
       </c>
       <c r="AQ347" t="inlineStr">
@@ -62347,14 +63051,9 @@
           <t>parity</t>
         </is>
       </c>
-      <c r="AR347" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
       <c r="AS347" t="inlineStr">
         <is>
-          <t>SER_KR_ANIMAL_INFLUENZA_HUMAN_INFECTION</t>
+          <t>SER_SG_CDA_AVIAN_INFLUENZA; SER_SG_HIST_AVIAN_INFLUENZA</t>
         </is>
       </c>
       <c r="AT347" t="n">
@@ -62362,47 +63061,47 @@
       </c>
       <c r="AU347" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV347" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW347" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX347" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY347" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ347" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA347" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB347" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC347" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -62434,12 +63133,12 @@
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G348" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H348" t="inlineStr">
@@ -62464,12 +63163,12 @@
       </c>
       <c r="L348" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="M348" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="N348" t="n">
@@ -62478,24 +63177,27 @@
       <c r="O348" t="n">
         <v>0</v>
       </c>
+      <c r="P348" t="n">
+        <v>0</v>
+      </c>
       <c r="U348" t="inlineStr">
         <is>
-          <t>SER_KR_ANIMAL_INFLUENZA_HUMAN_INFECTION</t>
+          <t>SER_SG_CDA_AVIAN_INFLUENZA</t>
         </is>
       </c>
       <c r="V348" t="inlineStr">
         <is>
-          <t>SER_KR_ANIMAL_INFLUENZA_HUMAN_INFECTION</t>
+          <t>SER_SG_CDA_AVIAN_INFLUENZA</t>
         </is>
       </c>
       <c r="W348" t="inlineStr">
         <is>
-          <t>SRC_KR_KDCA</t>
+          <t>SRC_SG_CDA_WIDB</t>
         </is>
       </c>
       <c r="X348" t="inlineStr">
         <is>
-          <t>동물인플루엔자 인체감염증</t>
+          <t>Avian Influenza</t>
         </is>
       </c>
       <c r="Y348" t="inlineStr">
@@ -62505,12 +63207,12 @@
       </c>
       <c r="Z348" t="inlineStr">
         <is>
-          <t>notification</t>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA348" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AB348" t="inlineStr">
@@ -62520,7 +63222,7 @@
       </c>
       <c r="AC348" t="inlineStr">
         <is>
-          <t>country:KR:national</t>
+          <t>country:SG:national</t>
         </is>
       </c>
       <c r="AD348" t="inlineStr">
@@ -62530,12 +63232,12 @@
       </c>
       <c r="AE348" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>narrower</t>
         </is>
       </c>
       <c r="AF348" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>conditional</t>
         </is>
       </c>
       <c r="AG348" t="inlineStr">
@@ -62555,12 +63257,12 @@
       </c>
       <c r="AJ348" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
         </is>
       </c>
       <c r="AK348" t="inlineStr">
         <is>
-          <t>Korea KDCA animal influenza infection in humans, retained separately from the generic novel influenza category.</t>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
         </is>
       </c>
       <c r="AM348" t="inlineStr">
@@ -62578,7 +63280,7 @@
       </c>
       <c r="AP348" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>temporal_handoff</t>
         </is>
       </c>
       <c r="AQ348" t="inlineStr">
@@ -62586,14 +63288,9 @@
           <t>parity</t>
         </is>
       </c>
-      <c r="AR348" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
       <c r="AS348" t="inlineStr">
         <is>
-          <t>SER_KR_ANIMAL_INFLUENZA_HUMAN_INFECTION</t>
+          <t>SER_SG_CDA_AVIAN_INFLUENZA; SER_SG_HIST_AVIAN_INFLUENZA</t>
         </is>
       </c>
       <c r="AT348" t="n">
@@ -62601,47 +63298,47 @@
       </c>
       <c r="AU348" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV348" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW348" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX348" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY348" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ348" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA348" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB348" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC348" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -62668,17 +63365,17 @@
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G349" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H349" t="inlineStr">
@@ -62703,12 +63400,12 @@
       </c>
       <c r="L349" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="M349" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="N349" t="n">
@@ -62717,170 +63414,76 @@
       <c r="O349" t="n">
         <v>0</v>
       </c>
-      <c r="U349" t="inlineStr">
-        <is>
-          <t>SER_KR_NOVEL_INFLUENZA</t>
-        </is>
-      </c>
-      <c r="V349" t="inlineStr">
-        <is>
-          <t>SER_KR_NOVEL_INFLUENZA</t>
-        </is>
-      </c>
-      <c r="W349" t="inlineStr">
-        <is>
-          <t>SRC_KR_KDCA</t>
-        </is>
-      </c>
-      <c r="X349" t="inlineStr">
-        <is>
-          <t>신종인플루엔자</t>
-        </is>
-      </c>
-      <c r="Y349" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z349" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
-      <c r="AA349" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB349" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC349" t="inlineStr">
-        <is>
-          <t>country:KR:national</t>
-        </is>
-      </c>
-      <c r="AD349" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE349" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF349" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG349" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH349" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI349" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ349" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
-        </is>
-      </c>
-      <c r="AK349" t="inlineStr">
-        <is>
-          <t>Korea KDCA novel influenza category.</t>
-        </is>
-      </c>
-      <c r="AM349" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN349" t="b">
-        <v>0</v>
+      <c r="R349" t="n">
+        <v>0</v>
+      </c>
+      <c r="S349" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO349" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP349" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ349" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR349" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS349" t="inlineStr">
-        <is>
-          <t>SER_KR_ANIMAL_INFLUENZA_HUMAN_INFECTION</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS349" t="inlineStr"/>
       <c r="AT349" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU349" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV349" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW349" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX349" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY349" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ349" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA349" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB349" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC349" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -62912,120 +63515,1550 @@
       </c>
       <c r="F350" t="inlineStr">
         <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G350" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H350" t="inlineStr">
+        <is>
+          <t>D016</t>
+        </is>
+      </c>
+      <c r="I350" t="inlineStr">
+        <is>
+          <t>Novel influenza A</t>
+        </is>
+      </c>
+      <c r="J350" t="inlineStr">
+        <is>
+          <t>人感染新亚型流感</t>
+        </is>
+      </c>
+      <c r="K350" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L350" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="M350" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N350" t="n">
+        <v>0</v>
+      </c>
+      <c r="O350" t="n">
+        <v>0</v>
+      </c>
+      <c r="P350" t="n">
+        <v>0</v>
+      </c>
+      <c r="R350" t="n">
+        <v>0</v>
+      </c>
+      <c r="S350" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA350" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO350" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP350" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ350" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS350" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_AVIAN_INFLUENZA; SER_SG_HIST_AVIAN_INFLUENZA</t>
+        </is>
+      </c>
+      <c r="AT350" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU350" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV350" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW350" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX350" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY350" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ350" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA350" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB350" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC350" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>D016</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>novel-influenza-a</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>Novel influenza A</t>
+        </is>
+      </c>
+      <c r="E351" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F351" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G351" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H351" t="inlineStr">
+        <is>
+          <t>D016</t>
+        </is>
+      </c>
+      <c r="I351" t="inlineStr">
+        <is>
+          <t>Novel influenza A</t>
+        </is>
+      </c>
+      <c r="J351" t="inlineStr">
+        <is>
+          <t>人感染新亚型流感</t>
+        </is>
+      </c>
+      <c r="K351" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L351" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="M351" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N351" t="n">
+        <v>0</v>
+      </c>
+      <c r="O351" t="n">
+        <v>0</v>
+      </c>
+      <c r="P351" t="n">
+        <v>0</v>
+      </c>
+      <c r="U351" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_AVIAN_INFLUENZA</t>
+        </is>
+      </c>
+      <c r="V351" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_AVIAN_INFLUENZA</t>
+        </is>
+      </c>
+      <c r="W351" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X351" t="inlineStr">
+        <is>
+          <t>Avian Influenza</t>
+        </is>
+      </c>
+      <c r="Y351" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z351" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA351" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB351" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC351" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD351" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE351" t="inlineStr">
+        <is>
+          <t>narrower</t>
+        </is>
+      </c>
+      <c r="AF351" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG351" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH351" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI351" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ351" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK351" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM351" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN351" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO351" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP351" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ351" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS351" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_AVIAN_INFLUENZA; SER_SG_HIST_AVIAN_INFLUENZA</t>
+        </is>
+      </c>
+      <c r="AT351" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU351" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV351" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW351" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX351" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY351" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ351" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA351" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB351" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC351" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>D016</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>novel-influenza-a</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>Novel influenza A</t>
+        </is>
+      </c>
+      <c r="E352" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F352" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G352" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H352" t="inlineStr">
+        <is>
+          <t>D016</t>
+        </is>
+      </c>
+      <c r="I352" t="inlineStr">
+        <is>
+          <t>Novel influenza A</t>
+        </is>
+      </c>
+      <c r="J352" t="inlineStr">
+        <is>
+          <t>人感染新亚型流感</t>
+        </is>
+      </c>
+      <c r="K352" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L352" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M352" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N352" t="n">
+        <v>0</v>
+      </c>
+      <c r="O352" t="n">
+        <v>0</v>
+      </c>
+      <c r="R352" t="n">
+        <v>0</v>
+      </c>
+      <c r="S352" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U352" t="inlineStr">
+        <is>
+          <t>SER_KR_ANIMAL_INFLUENZA_HUMAN_INFECTION</t>
+        </is>
+      </c>
+      <c r="AA352" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO352" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP352" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ352" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR352" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS352" t="inlineStr">
+        <is>
+          <t>SER_KR_ANIMAL_INFLUENZA_HUMAN_INFECTION</t>
+        </is>
+      </c>
+      <c r="AT352" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU352" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV352" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW352" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX352" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY352" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ352" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA352" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB352" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC352" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>D016</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>novel-influenza-a</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>Novel influenza A</t>
+        </is>
+      </c>
+      <c r="E353" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F353" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G353" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H353" t="inlineStr">
+        <is>
+          <t>D016</t>
+        </is>
+      </c>
+      <c r="I353" t="inlineStr">
+        <is>
+          <t>Novel influenza A</t>
+        </is>
+      </c>
+      <c r="J353" t="inlineStr">
+        <is>
+          <t>人感染新亚型流感</t>
+        </is>
+      </c>
+      <c r="K353" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L353" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M353" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N353" t="n">
+        <v>0</v>
+      </c>
+      <c r="O353" t="n">
+        <v>0</v>
+      </c>
+      <c r="U353" t="inlineStr">
+        <is>
+          <t>SER_KR_ANIMAL_INFLUENZA_HUMAN_INFECTION</t>
+        </is>
+      </c>
+      <c r="V353" t="inlineStr">
+        <is>
+          <t>SER_KR_ANIMAL_INFLUENZA_HUMAN_INFECTION</t>
+        </is>
+      </c>
+      <c r="W353" t="inlineStr">
+        <is>
+          <t>SRC_KR_KDCA</t>
+        </is>
+      </c>
+      <c r="X353" t="inlineStr">
+        <is>
+          <t>동물인플루엔자 인체감염증</t>
+        </is>
+      </c>
+      <c r="Y353" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z353" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA353" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB353" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC353" t="inlineStr">
+        <is>
+          <t>country:KR:national</t>
+        </is>
+      </c>
+      <c r="AD353" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE353" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF353" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG353" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH353" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI353" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ353" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
+        </is>
+      </c>
+      <c r="AK353" t="inlineStr">
+        <is>
+          <t>Korea KDCA animal influenza infection in humans, retained separately from the generic novel influenza category.</t>
+        </is>
+      </c>
+      <c r="AM353" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN353" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO353" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP353" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ353" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR353" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS353" t="inlineStr">
+        <is>
+          <t>SER_KR_ANIMAL_INFLUENZA_HUMAN_INFECTION</t>
+        </is>
+      </c>
+      <c r="AT353" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU353" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV353" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW353" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX353" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY353" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ353" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA353" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB353" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC353" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>D016</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>novel-influenza-a</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>Novel influenza A</t>
+        </is>
+      </c>
+      <c r="E354" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F354" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G354" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H354" t="inlineStr">
+        <is>
+          <t>D016</t>
+        </is>
+      </c>
+      <c r="I354" t="inlineStr">
+        <is>
+          <t>Novel influenza A</t>
+        </is>
+      </c>
+      <c r="J354" t="inlineStr">
+        <is>
+          <t>人感染新亚型流感</t>
+        </is>
+      </c>
+      <c r="K354" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L354" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M354" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N354" t="n">
+        <v>0</v>
+      </c>
+      <c r="O354" t="n">
+        <v>0</v>
+      </c>
+      <c r="U354" t="inlineStr">
+        <is>
+          <t>SER_KR_NOVEL_INFLUENZA</t>
+        </is>
+      </c>
+      <c r="V354" t="inlineStr">
+        <is>
+          <t>SER_KR_NOVEL_INFLUENZA</t>
+        </is>
+      </c>
+      <c r="W354" t="inlineStr">
+        <is>
+          <t>SRC_KR_KDCA</t>
+        </is>
+      </c>
+      <c r="X354" t="inlineStr">
+        <is>
+          <t>신종인플루엔자</t>
+        </is>
+      </c>
+      <c r="Y354" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z354" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA354" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB354" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC354" t="inlineStr">
+        <is>
+          <t>country:KR:national</t>
+        </is>
+      </c>
+      <c r="AD354" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE354" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF354" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG354" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH354" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI354" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ354" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
+        </is>
+      </c>
+      <c r="AK354" t="inlineStr">
+        <is>
+          <t>Korea KDCA novel influenza category.</t>
+        </is>
+      </c>
+      <c r="AM354" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN354" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO354" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP354" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ354" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR354" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS354" t="inlineStr">
+        <is>
+          <t>SER_KR_ANIMAL_INFLUENZA_HUMAN_INFECTION</t>
+        </is>
+      </c>
+      <c r="AT354" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU354" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV354" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW354" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX354" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY354" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ354" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA354" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB354" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC354" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>D016</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>novel-influenza-a</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>Novel influenza A</t>
+        </is>
+      </c>
+      <c r="E355" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F355" t="inlineStr">
+        <is>
           <t>JP</t>
         </is>
       </c>
-      <c r="G350" t="inlineStr">
+      <c r="G355" t="inlineStr">
         <is>
           <t>Japan</t>
         </is>
       </c>
-      <c r="H350" t="inlineStr">
-        <is>
-          <t>D016</t>
-        </is>
-      </c>
-      <c r="I350" t="inlineStr">
-        <is>
-          <t>Novel influenza A</t>
-        </is>
-      </c>
-      <c r="J350" t="inlineStr">
+      <c r="H355" t="inlineStr">
+        <is>
+          <t>D016</t>
+        </is>
+      </c>
+      <c r="I355" t="inlineStr">
+        <is>
+          <t>Novel influenza A</t>
+        </is>
+      </c>
+      <c r="J355" t="inlineStr">
         <is>
           <t>人感染新亚型流感</t>
         </is>
       </c>
-      <c r="K350" t="inlineStr">
+      <c r="K355" t="inlineStr">
         <is>
           <t>Viral</t>
         </is>
       </c>
-      <c r="L350" t="inlineStr">
+      <c r="L355" t="inlineStr">
         <is>
           <t>2026-10-04</t>
         </is>
       </c>
-      <c r="M350" t="inlineStr">
+      <c r="M355" t="inlineStr">
         <is>
           <t>2026-10</t>
         </is>
       </c>
-      <c r="N350" t="n">
-        <v>0</v>
-      </c>
-      <c r="O350" t="n">
-        <v>0</v>
-      </c>
-      <c r="R350" t="n">
-        <v>0</v>
-      </c>
-      <c r="S350" t="inlineStr">
+      <c r="N355" t="n">
+        <v>0</v>
+      </c>
+      <c r="O355" t="n">
+        <v>0</v>
+      </c>
+      <c r="R355" t="n">
+        <v>0</v>
+      </c>
+      <c r="S355" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AO350" t="inlineStr">
+      <c r="AO355" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AP350" t="inlineStr">
+      <c r="AP355" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AR350" t="inlineStr">
+      <c r="AR355" t="inlineStr">
         <is>
           <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
-      <c r="AS350" t="inlineStr"/>
-      <c r="AT350" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU350" t="inlineStr">
+      <c r="AS355" t="inlineStr"/>
+      <c r="AT355" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU355" t="inlineStr">
         <is>
           <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
-      <c r="AV350" t="inlineStr">
+      <c r="AV355" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="AW350" t="inlineStr">
+      <c r="AW355" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="AX350" t="inlineStr">
+      <c r="AX355" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="AY350" t="inlineStr">
+      <c r="AY355" t="inlineStr">
         <is>
           <t>web</t>
         </is>
       </c>
-      <c r="AZ350" t="inlineStr">
+      <c r="AZ355" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="BA350" t="inlineStr">
+      <c r="BA355" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="BB350" t="inlineStr">
+      <c r="BB355" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="BC350" t="inlineStr">
+      <c r="BC355" t="inlineStr">
         <is>
           <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>D016</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>novel-influenza-a</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>Novel influenza A</t>
+        </is>
+      </c>
+      <c r="E356" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F356" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G356" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H356" t="inlineStr">
+        <is>
+          <t>D016</t>
+        </is>
+      </c>
+      <c r="I356" t="inlineStr">
+        <is>
+          <t>Novel influenza A</t>
+        </is>
+      </c>
+      <c r="J356" t="inlineStr">
+        <is>
+          <t>人感染新亚型流感</t>
+        </is>
+      </c>
+      <c r="K356" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L356" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="M356" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N356" t="n">
+        <v>0</v>
+      </c>
+      <c r="O356" t="n">
+        <v>0</v>
+      </c>
+      <c r="P356" t="n">
+        <v>0</v>
+      </c>
+      <c r="R356" t="n">
+        <v>0</v>
+      </c>
+      <c r="S356" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA356" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO356" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP356" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ356" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS356" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_AVIAN_INFLUENZA; SER_SG_HIST_AVIAN_INFLUENZA</t>
+        </is>
+      </c>
+      <c r="AT356" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU356" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV356" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW356" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX356" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY356" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ356" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA356" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB356" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC356" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>D016</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>novel-influenza-a</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>Novel influenza A</t>
+        </is>
+      </c>
+      <c r="E357" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F357" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G357" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H357" t="inlineStr">
+        <is>
+          <t>D016</t>
+        </is>
+      </c>
+      <c r="I357" t="inlineStr">
+        <is>
+          <t>Novel influenza A</t>
+        </is>
+      </c>
+      <c r="J357" t="inlineStr">
+        <is>
+          <t>人感染新亚型流感</t>
+        </is>
+      </c>
+      <c r="K357" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L357" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="M357" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N357" t="n">
+        <v>0</v>
+      </c>
+      <c r="O357" t="n">
+        <v>0</v>
+      </c>
+      <c r="P357" t="n">
+        <v>0</v>
+      </c>
+      <c r="U357" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_AVIAN_INFLUENZA</t>
+        </is>
+      </c>
+      <c r="V357" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_AVIAN_INFLUENZA</t>
+        </is>
+      </c>
+      <c r="W357" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X357" t="inlineStr">
+        <is>
+          <t>Avian Influenza</t>
+        </is>
+      </c>
+      <c r="Y357" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z357" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA357" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB357" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC357" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD357" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE357" t="inlineStr">
+        <is>
+          <t>narrower</t>
+        </is>
+      </c>
+      <c r="AF357" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG357" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH357" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI357" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ357" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK357" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM357" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN357" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO357" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP357" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ357" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS357" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_AVIAN_INFLUENZA; SER_SG_HIST_AVIAN_INFLUENZA</t>
+        </is>
+      </c>
+      <c r="AT357" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU357" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV357" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW357" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX357" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY357" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ357" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA357" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB357" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC357" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -63145,7 +65178,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="10">
@@ -63155,7 +65188,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>349</v>
+        <v>356</v>
       </c>
     </row>
     <row r="11">
@@ -63175,7 +65208,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>111</v>
+        <v>116</v>
       </c>
     </row>
     <row r="13">
@@ -63185,7 +65218,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14">
@@ -63207,7 +65240,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="16">
